--- a/Results/model_summary/Model_Convergence_and_Parameters_Summary.xlsx
+++ b/Results/model_summary/Model_Convergence_and_Parameters_Summary.xlsx
@@ -796,18 +796,18 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>14087.4</v>
+        <v>14123.6</v>
       </c>
       <c r="H8">
-        <v>1445.7</v>
+        <v>1498</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[11588.9, 17266.5]</t>
+          <t>[11516.9, 17387.3]</t>
         </is>
       </c>
       <c r="J8">
-        <v>1.0817</v>
+        <v>1.0198</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Acceptable Convergence (Rhat &lt; 1.10)</t>
+          <t>Fully Converged (Rhat &lt; 1.05)</t>
         </is>
       </c>
     </row>
@@ -853,18 +853,18 @@
         <v>0.23</v>
       </c>
       <c r="G9">
-        <v>14087.4</v>
+        <v>14123.6</v>
       </c>
       <c r="H9">
-        <v>1445.7</v>
+        <v>1498</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[11588.9, 17266.5]</t>
+          <t>[11516.9, 17387.3]</t>
         </is>
       </c>
       <c r="J9">
-        <v>1.0817</v>
+        <v>1.0198</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Acceptable Convergence (Rhat &lt; 1.10)</t>
+          <t>Fully Converged (Rhat &lt; 1.05)</t>
         </is>
       </c>
     </row>
@@ -910,18 +910,18 @@
         <v>0.5</v>
       </c>
       <c r="G10">
-        <v>14087.4</v>
+        <v>14123.6</v>
       </c>
       <c r="H10">
-        <v>1445.7</v>
+        <v>1498</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[11588.9, 17266.5]</t>
+          <t>[11516.9, 17387.3]</t>
         </is>
       </c>
       <c r="J10">
-        <v>1.0817</v>
+        <v>1.0198</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Acceptable Convergence (Rhat &lt; 1.10)</t>
+          <t>Fully Converged (Rhat &lt; 1.05)</t>
         </is>
       </c>
     </row>
@@ -967,18 +967,18 @@
         <v>0.82</v>
       </c>
       <c r="G11">
-        <v>14087.4</v>
+        <v>14123.6</v>
       </c>
       <c r="H11">
-        <v>1445.7</v>
+        <v>1498</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[11588.9, 17266.5]</t>
+          <t>[11516.9, 17387.3]</t>
         </is>
       </c>
       <c r="J11">
-        <v>1.0817</v>
+        <v>1.0198</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Acceptable Convergence (Rhat &lt; 1.10)</t>
+          <t>Fully Converged (Rhat &lt; 1.05)</t>
         </is>
       </c>
     </row>
@@ -1024,18 +1024,18 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="G12">
-        <v>14087.4</v>
+        <v>14123.6</v>
       </c>
       <c r="H12">
-        <v>1445.7</v>
+        <v>1498</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[11588.9, 17266.5]</t>
+          <t>[11516.9, 17387.3]</t>
         </is>
       </c>
       <c r="J12">
-        <v>1.0817</v>
+        <v>1.0198</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Acceptable Convergence (Rhat &lt; 1.10)</t>
+          <t>Fully Converged (Rhat &lt; 1.05)</t>
         </is>
       </c>
     </row>
@@ -1081,18 +1081,18 @@
         <v>1.67</v>
       </c>
       <c r="G13">
-        <v>14087.4</v>
+        <v>14123.6</v>
       </c>
       <c r="H13">
-        <v>1445.7</v>
+        <v>1498</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[11588.9, 17266.5]</t>
+          <t>[11516.9, 17387.3]</t>
         </is>
       </c>
       <c r="J13">
-        <v>1.0817</v>
+        <v>1.0198</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Acceptable Convergence (Rhat &lt; 1.10)</t>
+          <t>Fully Converged (Rhat &lt; 1.05)</t>
         </is>
       </c>
     </row>
@@ -1138,27 +1138,27 @@
         <v>1.78</v>
       </c>
       <c r="G14">
-        <v>14027.3</v>
+        <v>14216</v>
       </c>
       <c r="H14">
-        <v>1363.4</v>
+        <v>1455.4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[11576.6, 16976.4]</t>
+          <t>[11752.4, 17451.8]</t>
         </is>
       </c>
       <c r="J14">
-        <v>1.0521</v>
+        <v>1.0242</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.0350</t>
+          <t>1.0182</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.3303</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -27146,31 +27146,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>1.589311306603231</v>
+        <v>1.589395984848507</v>
       </c>
       <c r="H2">
-        <v>0.007205628292603781</v>
+        <v>0.007262318948204624</v>
       </c>
       <c r="I2">
-        <v>0.0002252675616788616</v>
+        <v>0.0001460825366373568</v>
       </c>
       <c r="J2">
-        <v>1023.2</v>
+        <v>2471.5</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L2">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M2">
-        <v>1.587119633634973</v>
+        <v>1.587220493981195</v>
       </c>
       <c r="N2">
-        <v>1.582167677340778</v>
+        <v>1.582191212529661</v>
       </c>
       <c r="O2">
-        <v>1.608904274809916</v>
+        <v>1.608928520286697</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -27208,35 +27208,35 @@
         </is>
       </c>
       <c r="G3">
-        <v>14087.40902959247</v>
+        <v>14123.64149129999</v>
       </c>
       <c r="H3">
-        <v>1445.727510630541</v>
+        <v>1498.001853014637</v>
       </c>
       <c r="I3">
-        <v>52.71048431542673</v>
+        <v>36.50273536976891</v>
       </c>
       <c r="J3">
-        <v>752.3</v>
+        <v>1684.1</v>
       </c>
       <c r="K3">
-        <v>1.0016</v>
+        <v>1.0007</v>
       </c>
       <c r="L3">
-        <v>1.0018</v>
+        <v>1.0008</v>
       </c>
       <c r="M3">
-        <v>13992.38790436515</v>
+        <v>14004.29100480898</v>
       </c>
       <c r="N3">
-        <v>11588.8616471647</v>
+        <v>11516.91198988923</v>
       </c>
       <c r="O3">
-        <v>17266.52511340762</v>
+        <v>17387.29688123515</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[11588.8616, 17266.5251]</t>
+          <t>[11516.9120, 17387.2969]</t>
         </is>
       </c>
     </row>
@@ -27270,35 +27270,35 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.3113032558764295</v>
+        <v>0.3232031014683357</v>
       </c>
       <c r="H4">
-        <v>0.1362093634617424</v>
+        <v>0.1420946102486272</v>
       </c>
       <c r="I4">
-        <v>0.007187725811170085</v>
+        <v>0.005248126246874685</v>
       </c>
       <c r="J4">
-        <v>359.1</v>
+        <v>733.1</v>
       </c>
       <c r="K4">
-        <v>1.021</v>
+        <v>1.0073</v>
       </c>
       <c r="L4">
-        <v>1.0212</v>
+        <v>1.0074</v>
       </c>
       <c r="M4">
-        <v>0.316257303341141</v>
+        <v>0.329737376709393</v>
       </c>
       <c r="N4">
-        <v>0.02694270680745655</v>
+        <v>0.02380958686559168</v>
       </c>
       <c r="O4">
-        <v>0.5693657637896794</v>
+        <v>0.5866353602915522</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[0.0269, 0.5694]</t>
+          <t>[0.0238, 0.5866]</t>
         </is>
       </c>
     </row>
@@ -27332,35 +27332,35 @@
         </is>
       </c>
       <c r="G5">
-        <v>-0.1161112990728373</v>
+        <v>-0.1287407946727498</v>
       </c>
       <c r="H5">
-        <v>0.1148021978489128</v>
+        <v>0.1205661088449834</v>
       </c>
       <c r="I5">
-        <v>0.004777383282242065</v>
+        <v>0.003673175758948686</v>
       </c>
       <c r="J5">
-        <v>577.5</v>
+        <v>1077.4</v>
       </c>
       <c r="K5">
-        <v>1.0004</v>
+        <v>1.0005</v>
       </c>
       <c r="L5">
         <v>1.0006</v>
       </c>
       <c r="M5">
-        <v>-0.1133521931553859</v>
+        <v>-0.1273749279336696</v>
       </c>
       <c r="N5">
-        <v>-0.3386719515336633</v>
+        <v>-0.3651564914560492</v>
       </c>
       <c r="O5">
-        <v>0.1091078866312331</v>
+        <v>0.1069579387757273</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[-0.3387, 0.1091]</t>
+          <t>[-0.3652, 0.1070]</t>
         </is>
       </c>
     </row>
@@ -27394,35 +27394,35 @@
         </is>
       </c>
       <c r="G6">
-        <v>-0.5116146559729645</v>
+        <v>-0.5369591626463901</v>
       </c>
       <c r="H6">
-        <v>0.1871635112221394</v>
+        <v>0.2036126439218424</v>
       </c>
       <c r="I6">
-        <v>0.01356939193655912</v>
+        <v>0.009715251156275482</v>
       </c>
       <c r="J6">
-        <v>190.2</v>
+        <v>439.2</v>
       </c>
       <c r="K6">
-        <v>1.0055</v>
+        <v>1.005</v>
       </c>
       <c r="L6">
-        <v>1.0057</v>
+        <v>1.005</v>
       </c>
       <c r="M6">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="N6">
-        <v>-0.8514261295155847</v>
+        <v>-0.9272919620447222</v>
       </c>
       <c r="O6">
-        <v>-0.1024529610643907</v>
+        <v>-0.1120617046669647</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[-0.8514, -0.1025]</t>
+          <t>[-0.9273, -0.1121]</t>
         </is>
       </c>
     </row>
@@ -27456,35 +27456,35 @@
         </is>
       </c>
       <c r="G7">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="H7">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="I7">
-        <v>0.005794357245884296</v>
+        <v>0.004167663529072831</v>
       </c>
       <c r="J7">
-        <v>433.1</v>
+        <v>926.6</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>1.0017</v>
       </c>
       <c r="L7">
-        <v>1.0001</v>
+        <v>1.0017</v>
       </c>
       <c r="M7">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="N7">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="O7">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>[-0.5470, -0.0704]</t>
+          <t>[-0.5529, -0.0508]</t>
         </is>
       </c>
     </row>
@@ -27518,35 +27518,35 @@
         </is>
       </c>
       <c r="G8">
-        <v>-1.666137154963477</v>
+        <v>-1.676201540987581</v>
       </c>
       <c r="H8">
-        <v>1.030182074355619</v>
+        <v>1.035283833008518</v>
       </c>
       <c r="I8">
-        <v>0.100866393262972</v>
+        <v>0.06791265277941498</v>
       </c>
       <c r="J8">
-        <v>104.3</v>
+        <v>232.4</v>
       </c>
       <c r="K8">
-        <v>1.0817</v>
+        <v>1.0198</v>
       </c>
       <c r="L8">
-        <v>1.0819</v>
+        <v>1.0199</v>
       </c>
       <c r="M8">
-        <v>-1.628339858179879</v>
+        <v>-1.675147167474839</v>
       </c>
       <c r="N8">
-        <v>-3.870161755723977</v>
+        <v>-3.805123165114205</v>
       </c>
       <c r="O8">
-        <v>0.1267385224481098</v>
+        <v>0.1771553118029174</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[-3.8702, 0.1267]</t>
+          <t>[-3.8051, 0.1772]</t>
         </is>
       </c>
     </row>
@@ -27580,35 +27580,35 @@
         </is>
       </c>
       <c r="G9">
-        <v>0.06196936670816747</v>
+        <v>0.06535679301344875</v>
       </c>
       <c r="H9">
-        <v>0.0772600688734436</v>
+        <v>0.07677840040677844</v>
       </c>
       <c r="I9">
-        <v>0.002160805820487455</v>
+        <v>0.001474194024410116</v>
       </c>
       <c r="J9">
-        <v>1278.4</v>
+        <v>2712.5</v>
       </c>
       <c r="K9">
-        <v>1.0072</v>
+        <v>1.0006</v>
       </c>
       <c r="L9">
-        <v>1.0074</v>
+        <v>1.0007</v>
       </c>
       <c r="M9">
-        <v>0.06586546619170625</v>
+        <v>0.0686554630567057</v>
       </c>
       <c r="N9">
-        <v>-0.09540206644877555</v>
+        <v>-0.09582465412121587</v>
       </c>
       <c r="O9">
-        <v>0.2074720015902419</v>
+        <v>0.2083591378841529</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>[-0.0954, 0.2075]</t>
+          <t>[-0.0958, 0.2084]</t>
         </is>
       </c>
     </row>
@@ -27642,16 +27642,16 @@
         </is>
       </c>
       <c r="G10">
-        <v>-0.1046798152858951</v>
+        <v>-0.107017835387122</v>
       </c>
       <c r="H10">
-        <v>0.1301398294968226</v>
+        <v>0.1269459264510429</v>
       </c>
       <c r="I10">
-        <v>0.004153229807695243</v>
+        <v>0.002331311468511136</v>
       </c>
       <c r="J10">
-        <v>981.9</v>
+        <v>2965.1</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -27660,17 +27660,17 @@
         <v>1.0001</v>
       </c>
       <c r="M10">
-        <v>-0.1004581502557295</v>
+        <v>-0.1023315305345405</v>
       </c>
       <c r="N10">
-        <v>-0.3753464505385751</v>
+        <v>-0.3681489359962021</v>
       </c>
       <c r="O10">
-        <v>0.135475681257319</v>
+        <v>0.1248289554633815</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>[-0.3753, 0.1355]</t>
+          <t>[-0.3681, 0.1248]</t>
         </is>
       </c>
     </row>
@@ -27704,35 +27704,35 @@
         </is>
       </c>
       <c r="G11">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="H11">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="I11">
-        <v>0.02436067252164474</v>
+        <v>0.01616118574776551</v>
       </c>
       <c r="J11">
-        <v>104.3</v>
+        <v>243</v>
       </c>
       <c r="K11">
-        <v>1.0628</v>
+        <v>1.0136</v>
       </c>
       <c r="L11">
-        <v>1.063</v>
+        <v>1.0137</v>
       </c>
       <c r="M11">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="N11">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="O11">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>[-0.0167, 0.9905]</t>
+          <t>[0.0128, 1.0033]</t>
         </is>
       </c>
     </row>
@@ -27766,31 +27766,31 @@
         </is>
       </c>
       <c r="G12">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="H12">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="I12">
-        <v>7.424757282131184E-05</v>
+        <v>4.810704063421389E-05</v>
       </c>
       <c r="J12">
-        <v>1024.3</v>
+        <v>2479</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L12">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M12">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="N12">
-        <v>0.6577796351508191</v>
+        <v>0.6577717760918227</v>
       </c>
       <c r="O12">
-        <v>0.666602501839997</v>
+        <v>0.6665945953183382</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -27828,31 +27828,31 @@
         </is>
       </c>
       <c r="G13">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="H13">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="I13">
-        <v>7.424757282131176E-05</v>
+        <v>4.810704063421387E-05</v>
       </c>
       <c r="J13">
-        <v>1024.3</v>
+        <v>2479</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L13">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M13">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="N13">
-        <v>0.333397498160003</v>
+        <v>0.3334054046816618</v>
       </c>
       <c r="O13">
-        <v>0.342220364849181</v>
+        <v>0.3422282239081773</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -27890,35 +27890,35 @@
         </is>
       </c>
       <c r="G14">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="H14">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="I14">
-        <v>0.000338960358430166</v>
+        <v>0.0002197621614077366</v>
       </c>
       <c r="J14">
-        <v>1023.5</v>
+        <v>2473.4</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L14">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M14">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="N14">
-        <v>1.000288769513282</v>
+        <v>1.000324356132659</v>
       </c>
       <c r="O14">
-        <v>1.040531954963664</v>
+        <v>1.040568283247922</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[1.0003, 1.0405]</t>
+          <t>[1.0003, 1.0406]</t>
         </is>
       </c>
     </row>
@@ -27952,16 +27952,16 @@
         </is>
       </c>
       <c r="G15">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="H15">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="I15">
-        <v>0.0003294579253450585</v>
+        <v>0.0002222946018841949</v>
       </c>
       <c r="J15">
-        <v>947</v>
+        <v>2327.8</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -27970,17 +27970,17 @@
         <v>1.0001</v>
       </c>
       <c r="M15">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="N15">
-        <v>0.0002449518806358951</v>
+        <v>0.0002856212000216427</v>
       </c>
       <c r="O15">
-        <v>0.03625229849217988</v>
+        <v>0.04007699114601319</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[0.0002, 0.0363]</t>
+          <t>[0.0003, 0.0401]</t>
         </is>
       </c>
     </row>
@@ -28014,35 +28014,35 @@
         </is>
       </c>
       <c r="G16">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="H16">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="I16">
-        <v>1.996910908670789E-05</v>
+        <v>1.30210617703425E-05</v>
       </c>
       <c r="J16">
-        <v>1344.2</v>
+        <v>3318</v>
       </c>
       <c r="K16">
-        <v>1.0016</v>
+        <v>1.0007</v>
       </c>
       <c r="L16">
-        <v>1.0018</v>
+        <v>1.0008</v>
       </c>
       <c r="M16">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="N16">
-        <v>0.1242406376004758</v>
+        <v>0.1242264614416188</v>
       </c>
       <c r="O16">
-        <v>0.1270980490776865</v>
+        <v>0.1271816029686873</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>[0.1242, 0.1271]</t>
+          <t>[0.1242, 0.1272]</t>
         </is>
       </c>
     </row>
@@ -28076,31 +28076,31 @@
         </is>
       </c>
       <c r="G17">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="H17">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="I17">
-        <v>1.683505527229803E-05</v>
+        <v>1.020921344739324E-05</v>
       </c>
       <c r="J17">
-        <v>1041.4</v>
+        <v>2851.2</v>
       </c>
       <c r="K17">
-        <v>1.0008</v>
+        <v>1.0003</v>
       </c>
       <c r="L17">
-        <v>1.0009</v>
+        <v>1.0003</v>
       </c>
       <c r="M17">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="N17">
-        <v>0.06283446095178546</v>
+        <v>0.06283477689587211</v>
       </c>
       <c r="O17">
-        <v>0.06498835543089833</v>
+        <v>0.06500131971690672</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -28138,35 +28138,35 @@
         </is>
       </c>
       <c r="G18">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="H18">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="I18">
-        <v>7.287717726856617E-05</v>
+        <v>4.844680439743285E-05</v>
       </c>
       <c r="J18">
-        <v>1607</v>
+        <v>3850.4</v>
       </c>
       <c r="K18">
-        <v>1.0027</v>
+        <v>1.0002</v>
       </c>
       <c r="L18">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M18">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="N18">
-        <v>0.08530357549931405</v>
+        <v>0.08530411553282874</v>
       </c>
       <c r="O18">
-        <v>0.09676944586807242</v>
+        <v>0.09708120921233582</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>[0.0853, 0.0968]</t>
+          <t>[0.0853, 0.0971]</t>
         </is>
       </c>
     </row>
@@ -28200,31 +28200,31 @@
         </is>
       </c>
       <c r="G19">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="H19">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="I19">
-        <v>3.986943120105059E-05</v>
+        <v>2.631252420617495E-05</v>
       </c>
       <c r="J19">
-        <v>1488.3</v>
+        <v>3549.4</v>
       </c>
       <c r="K19">
-        <v>1.0026</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="M19">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="N19">
-        <v>0.04340335790008991</v>
+        <v>0.04337718702816454</v>
       </c>
       <c r="O19">
-        <v>0.04949428357228296</v>
+        <v>0.04953662420187081</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -28262,35 +28262,35 @@
         </is>
       </c>
       <c r="G20">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="H20">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="I20">
-        <v>0.0001029288770320282</v>
+        <v>6.927062815829008E-05</v>
       </c>
       <c r="J20">
-        <v>1613</v>
+        <v>3780.6</v>
       </c>
       <c r="K20">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="L20">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M20">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="N20">
-        <v>0.03999117999120268</v>
+        <v>0.03994847125857982</v>
       </c>
       <c r="O20">
-        <v>0.05616933018720535</v>
+        <v>0.05673759616221472</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>[0.0400, 0.0562]</t>
+          <t>[0.0399, 0.0567]</t>
         </is>
       </c>
     </row>
@@ -28324,35 +28324,35 @@
         </is>
       </c>
       <c r="G21">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="H21">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="I21">
-        <v>5.51738195653668E-05</v>
+        <v>3.693842765066764E-05</v>
       </c>
       <c r="J21">
-        <v>1543.5</v>
+        <v>3616</v>
       </c>
       <c r="K21">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L21">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M21">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="N21">
-        <v>0.02064486387576463</v>
+        <v>0.02057363057052737</v>
       </c>
       <c r="O21">
-        <v>0.02922876830495247</v>
+        <v>0.02929047714320697</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>[0.0206, 0.0292]</t>
+          <t>[0.0206, 0.0293]</t>
         </is>
       </c>
     </row>
@@ -28386,35 +28386,35 @@
         </is>
       </c>
       <c r="G22">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="H22">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="I22">
-        <v>7.654870579497798E-05</v>
+        <v>5.163247376084753E-05</v>
       </c>
       <c r="J22">
-        <v>1618.5</v>
+        <v>3800.1</v>
       </c>
       <c r="K22">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L22">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M22">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="N22">
-        <v>0.01283181136513961</v>
+        <v>0.01279121060028293</v>
       </c>
       <c r="O22">
-        <v>0.02486300206783066</v>
+        <v>0.02534096888804091</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>[0.0128, 0.0249]</t>
+          <t>[0.0128, 0.0253]</t>
         </is>
       </c>
     </row>
@@ -28448,35 +28448,35 @@
         </is>
       </c>
       <c r="G23">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="H23">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="I23">
-        <v>4.173482703340465E-05</v>
+        <v>2.809001079626773E-05</v>
       </c>
       <c r="J23">
-        <v>1549.7</v>
+        <v>3629</v>
       </c>
       <c r="K23">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L23">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M23">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="N23">
-        <v>0.006754465912628241</v>
+        <v>0.006711515300852532</v>
       </c>
       <c r="O23">
-        <v>0.01324374278248805</v>
+        <v>0.01334017469519632</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>[0.0068, 0.0132]</t>
+          <t>[0.0067, 0.0133]</t>
         </is>
       </c>
     </row>
@@ -28510,35 +28510,35 @@
         </is>
       </c>
       <c r="G24">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="H24">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="I24">
-        <v>3.545284751407308E-05</v>
+        <v>2.416065724367434E-05</v>
       </c>
       <c r="J24">
-        <v>1631.4</v>
+        <v>3795.6</v>
       </c>
       <c r="K24">
-        <v>1.0025</v>
+        <v>1.0001</v>
       </c>
       <c r="L24">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="M24">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="N24">
-        <v>0.002821790209533828</v>
+        <v>0.002799332792224822</v>
       </c>
       <c r="O24">
-        <v>0.008395180840575273</v>
+        <v>0.008648722296811141</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>[0.0028, 0.0084]</t>
+          <t>[0.0028, 0.0086]</t>
         </is>
       </c>
     </row>
@@ -28572,35 +28572,35 @@
         </is>
       </c>
       <c r="G25">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="H25">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="I25">
-        <v>1.984959082910289E-05</v>
+        <v>1.348852967546526E-05</v>
       </c>
       <c r="J25">
-        <v>1560.3</v>
+        <v>3641.1</v>
       </c>
       <c r="K25">
-        <v>1.0025</v>
+        <v>1.0001</v>
       </c>
       <c r="L25">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="M25">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="N25">
-        <v>0.001519424188693608</v>
+        <v>0.00150537464286404</v>
       </c>
       <c r="O25">
-        <v>0.004612211856696236</v>
+        <v>0.004672985536810267</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>[0.0015, 0.0046]</t>
+          <t>[0.0015, 0.0047]</t>
         </is>
       </c>
     </row>
@@ -28634,35 +28634,35 @@
         </is>
       </c>
       <c r="G26">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="H26">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="I26">
-        <v>0.0378516379781366</v>
+        <v>0.02550205715002106</v>
       </c>
       <c r="J26">
-        <v>1614.6</v>
+        <v>3787.6</v>
       </c>
       <c r="K26">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L26">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M26">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="N26">
-        <v>31.99254556149809</v>
+        <v>31.94745644144655</v>
       </c>
       <c r="O26">
-        <v>37.93542068119201</v>
+        <v>38.14741835772089</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>[31.9925, 37.9354]</t>
+          <t>[31.9475, 38.1474]</t>
         </is>
       </c>
     </row>
@@ -28696,35 +28696,35 @@
         </is>
       </c>
       <c r="G27">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="H27">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="I27">
-        <v>0.04030004615481509</v>
+        <v>0.02712816536419896</v>
       </c>
       <c r="J27">
-        <v>1551.4</v>
+        <v>3630.6</v>
       </c>
       <c r="K27">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L27">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M27">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="N27">
-        <v>32.24875528724777</v>
+        <v>32.21258652369725</v>
       </c>
       <c r="O27">
-        <v>38.52489088509614</v>
+        <v>38.63563343246012</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>[32.2488, 38.5249]</t>
+          <t>[32.2126, 38.6356]</t>
         </is>
       </c>
     </row>
@@ -28758,35 +28758,35 @@
         </is>
       </c>
       <c r="G28">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="H28">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="I28">
-        <v>0.001085847783755566</v>
+        <v>0.0007306544822292565</v>
       </c>
       <c r="J28">
-        <v>1612.6</v>
+        <v>3778.7</v>
       </c>
       <c r="K28">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="L28">
-        <v>1.0029</v>
+        <v>1.0002</v>
       </c>
       <c r="M28">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="N28">
-        <v>3.465502924459196</v>
+        <v>3.464092567052742</v>
       </c>
       <c r="O28">
-        <v>3.635885258255161</v>
+        <v>3.641458084607688</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>[3.4655, 3.6359]</t>
+          <t>[3.4641, 3.6415]</t>
         </is>
       </c>
     </row>
@@ -28820,31 +28820,31 @@
         </is>
       </c>
       <c r="G29">
-        <v>1.589311306603231</v>
+        <v>1.589395984848507</v>
       </c>
       <c r="H29">
-        <v>0.007205628292603781</v>
+        <v>0.007262318948204624</v>
       </c>
       <c r="I29">
-        <v>0.0002252675616788616</v>
+        <v>0.0001460825366373568</v>
       </c>
       <c r="J29">
-        <v>1023.2</v>
+        <v>2471.5</v>
       </c>
       <c r="K29">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L29">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M29">
-        <v>1.587119633634973</v>
+        <v>1.587220493981195</v>
       </c>
       <c r="N29">
-        <v>1.582167677340778</v>
+        <v>1.582191212529661</v>
       </c>
       <c r="O29">
-        <v>1.608904274809916</v>
+        <v>1.608928520286697</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -28882,35 +28882,35 @@
         </is>
       </c>
       <c r="G30">
-        <v>14087.40902959247</v>
+        <v>14123.64149129999</v>
       </c>
       <c r="H30">
-        <v>1445.727510630541</v>
+        <v>1498.001853014637</v>
       </c>
       <c r="I30">
-        <v>52.71048431542673</v>
+        <v>36.50273536976891</v>
       </c>
       <c r="J30">
-        <v>752.3</v>
+        <v>1684.1</v>
       </c>
       <c r="K30">
-        <v>1.0016</v>
+        <v>1.0007</v>
       </c>
       <c r="L30">
-        <v>1.0018</v>
+        <v>1.0008</v>
       </c>
       <c r="M30">
-        <v>13992.38790436515</v>
+        <v>14004.29100480898</v>
       </c>
       <c r="N30">
-        <v>11588.8616471647</v>
+        <v>11516.91198988923</v>
       </c>
       <c r="O30">
-        <v>17266.52511340762</v>
+        <v>17387.29688123515</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>[11588.8616, 17266.5251]</t>
+          <t>[11516.9120, 17387.2969]</t>
         </is>
       </c>
     </row>
@@ -28944,35 +28944,35 @@
         </is>
       </c>
       <c r="G31">
-        <v>0.3113032558764295</v>
+        <v>0.3232031014683357</v>
       </c>
       <c r="H31">
-        <v>0.1362093634617424</v>
+        <v>0.1420946102486272</v>
       </c>
       <c r="I31">
-        <v>0.007187725811170085</v>
+        <v>0.005248126246874685</v>
       </c>
       <c r="J31">
-        <v>359.1</v>
+        <v>733.1</v>
       </c>
       <c r="K31">
-        <v>1.021</v>
+        <v>1.0073</v>
       </c>
       <c r="L31">
-        <v>1.0212</v>
+        <v>1.0074</v>
       </c>
       <c r="M31">
-        <v>0.316257303341141</v>
+        <v>0.329737376709393</v>
       </c>
       <c r="N31">
-        <v>0.02694270680745655</v>
+        <v>0.02380958686559168</v>
       </c>
       <c r="O31">
-        <v>0.5693657637896794</v>
+        <v>0.5866353602915522</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>[0.0269, 0.5694]</t>
+          <t>[0.0238, 0.5866]</t>
         </is>
       </c>
     </row>
@@ -29006,35 +29006,35 @@
         </is>
       </c>
       <c r="G32">
-        <v>-0.1161112990728373</v>
+        <v>-0.1287407946727498</v>
       </c>
       <c r="H32">
-        <v>0.1148021978489128</v>
+        <v>0.1205661088449834</v>
       </c>
       <c r="I32">
-        <v>0.004777383282242065</v>
+        <v>0.003673175758948686</v>
       </c>
       <c r="J32">
-        <v>577.5</v>
+        <v>1077.4</v>
       </c>
       <c r="K32">
-        <v>1.0004</v>
+        <v>1.0005</v>
       </c>
       <c r="L32">
         <v>1.0006</v>
       </c>
       <c r="M32">
-        <v>-0.1133521931553859</v>
+        <v>-0.1273749279336696</v>
       </c>
       <c r="N32">
-        <v>-0.3386719515336633</v>
+        <v>-0.3651564914560492</v>
       </c>
       <c r="O32">
-        <v>0.1091078866312331</v>
+        <v>0.1069579387757273</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>[-0.3387, 0.1091]</t>
+          <t>[-0.3652, 0.1070]</t>
         </is>
       </c>
     </row>
@@ -29068,35 +29068,35 @@
         </is>
       </c>
       <c r="G33">
-        <v>-0.5116146559729645</v>
+        <v>-0.5369591626463901</v>
       </c>
       <c r="H33">
-        <v>0.1871635112221394</v>
+        <v>0.2036126439218424</v>
       </c>
       <c r="I33">
-        <v>0.01356939193655912</v>
+        <v>0.009715251156275482</v>
       </c>
       <c r="J33">
-        <v>190.2</v>
+        <v>439.2</v>
       </c>
       <c r="K33">
-        <v>1.0055</v>
+        <v>1.005</v>
       </c>
       <c r="L33">
-        <v>1.0057</v>
+        <v>1.005</v>
       </c>
       <c r="M33">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="N33">
-        <v>-0.8514261295155847</v>
+        <v>-0.9272919620447222</v>
       </c>
       <c r="O33">
-        <v>-0.1024529610643907</v>
+        <v>-0.1120617046669647</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>[-0.8514, -0.1025]</t>
+          <t>[-0.9273, -0.1121]</t>
         </is>
       </c>
     </row>
@@ -29130,35 +29130,35 @@
         </is>
       </c>
       <c r="G34">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="H34">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="I34">
-        <v>0.005794357245884296</v>
+        <v>0.004167663529072831</v>
       </c>
       <c r="J34">
-        <v>433.1</v>
+        <v>926.6</v>
       </c>
       <c r="K34">
-        <v>1</v>
+        <v>1.0017</v>
       </c>
       <c r="L34">
-        <v>1.0001</v>
+        <v>1.0017</v>
       </c>
       <c r="M34">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="N34">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="O34">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>[-0.5470, -0.0704]</t>
+          <t>[-0.5529, -0.0508]</t>
         </is>
       </c>
     </row>
@@ -29192,35 +29192,35 @@
         </is>
       </c>
       <c r="G35">
-        <v>-1.666137154963477</v>
+        <v>-1.676201540987581</v>
       </c>
       <c r="H35">
-        <v>1.030182074355619</v>
+        <v>1.035283833008518</v>
       </c>
       <c r="I35">
-        <v>0.100866393262972</v>
+        <v>0.06791265277941498</v>
       </c>
       <c r="J35">
-        <v>104.3</v>
+        <v>232.4</v>
       </c>
       <c r="K35">
-        <v>1.0817</v>
+        <v>1.0198</v>
       </c>
       <c r="L35">
-        <v>1.0819</v>
+        <v>1.0199</v>
       </c>
       <c r="M35">
-        <v>-1.628339858179879</v>
+        <v>-1.675147167474839</v>
       </c>
       <c r="N35">
-        <v>-3.870161755723977</v>
+        <v>-3.805123165114205</v>
       </c>
       <c r="O35">
-        <v>0.1267385224481098</v>
+        <v>0.1771553118029174</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>[-3.8702, 0.1267]</t>
+          <t>[-3.8051, 0.1772]</t>
         </is>
       </c>
     </row>
@@ -29254,35 +29254,35 @@
         </is>
       </c>
       <c r="G36">
-        <v>0.06196936670816747</v>
+        <v>0.06535679301344875</v>
       </c>
       <c r="H36">
-        <v>0.0772600688734436</v>
+        <v>0.07677840040677844</v>
       </c>
       <c r="I36">
-        <v>0.002160805820487455</v>
+        <v>0.001474194024410116</v>
       </c>
       <c r="J36">
-        <v>1278.4</v>
+        <v>2712.5</v>
       </c>
       <c r="K36">
-        <v>1.0072</v>
+        <v>1.0006</v>
       </c>
       <c r="L36">
-        <v>1.0074</v>
+        <v>1.0007</v>
       </c>
       <c r="M36">
-        <v>0.06586546619170625</v>
+        <v>0.0686554630567057</v>
       </c>
       <c r="N36">
-        <v>-0.09540206644877555</v>
+        <v>-0.09582465412121587</v>
       </c>
       <c r="O36">
-        <v>0.2074720015902419</v>
+        <v>0.2083591378841529</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>[-0.0954, 0.2075]</t>
+          <t>[-0.0958, 0.2084]</t>
         </is>
       </c>
     </row>
@@ -29316,16 +29316,16 @@
         </is>
       </c>
       <c r="G37">
-        <v>-0.1046798152858951</v>
+        <v>-0.107017835387122</v>
       </c>
       <c r="H37">
-        <v>0.1301398294968226</v>
+        <v>0.1269459264510429</v>
       </c>
       <c r="I37">
-        <v>0.004153229807695243</v>
+        <v>0.002331311468511136</v>
       </c>
       <c r="J37">
-        <v>981.9</v>
+        <v>2965.1</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -29334,17 +29334,17 @@
         <v>1.0001</v>
       </c>
       <c r="M37">
-        <v>-0.1004581502557295</v>
+        <v>-0.1023315305345405</v>
       </c>
       <c r="N37">
-        <v>-0.3753464505385751</v>
+        <v>-0.3681489359962021</v>
       </c>
       <c r="O37">
-        <v>0.135475681257319</v>
+        <v>0.1248289554633815</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>[-0.3753, 0.1355]</t>
+          <t>[-0.3681, 0.1248]</t>
         </is>
       </c>
     </row>
@@ -29378,35 +29378,35 @@
         </is>
       </c>
       <c r="G38">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="H38">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="I38">
-        <v>0.02436067252164474</v>
+        <v>0.01616118574776551</v>
       </c>
       <c r="J38">
-        <v>104.3</v>
+        <v>243</v>
       </c>
       <c r="K38">
-        <v>1.0628</v>
+        <v>1.0136</v>
       </c>
       <c r="L38">
-        <v>1.063</v>
+        <v>1.0137</v>
       </c>
       <c r="M38">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="N38">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="O38">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>[-0.0167, 0.9905]</t>
+          <t>[0.0128, 1.0033]</t>
         </is>
       </c>
     </row>
@@ -29440,31 +29440,31 @@
         </is>
       </c>
       <c r="G39">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="H39">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="I39">
-        <v>7.424757282131184E-05</v>
+        <v>4.810704063421389E-05</v>
       </c>
       <c r="J39">
-        <v>1024.3</v>
+        <v>2479</v>
       </c>
       <c r="K39">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L39">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M39">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="N39">
-        <v>0.6577796351508191</v>
+        <v>0.6577717760918227</v>
       </c>
       <c r="O39">
-        <v>0.666602501839997</v>
+        <v>0.6665945953183382</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -29502,31 +29502,31 @@
         </is>
       </c>
       <c r="G40">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="H40">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="I40">
-        <v>7.424757282131176E-05</v>
+        <v>4.810704063421387E-05</v>
       </c>
       <c r="J40">
-        <v>1024.3</v>
+        <v>2479</v>
       </c>
       <c r="K40">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L40">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M40">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="N40">
-        <v>0.333397498160003</v>
+        <v>0.3334054046816618</v>
       </c>
       <c r="O40">
-        <v>0.342220364849181</v>
+        <v>0.3422282239081773</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -29564,35 +29564,35 @@
         </is>
       </c>
       <c r="G41">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="H41">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="I41">
-        <v>0.000338960358430166</v>
+        <v>0.0002197621614077366</v>
       </c>
       <c r="J41">
-        <v>1023.5</v>
+        <v>2473.4</v>
       </c>
       <c r="K41">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L41">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M41">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="N41">
-        <v>1.000288769513282</v>
+        <v>1.000324356132659</v>
       </c>
       <c r="O41">
-        <v>1.040531954963664</v>
+        <v>1.040568283247922</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>[1.0003, 1.0405]</t>
+          <t>[1.0003, 1.0406]</t>
         </is>
       </c>
     </row>
@@ -29626,16 +29626,16 @@
         </is>
       </c>
       <c r="G42">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="H42">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="I42">
-        <v>0.0003294579253450585</v>
+        <v>0.0002222946018841949</v>
       </c>
       <c r="J42">
-        <v>947</v>
+        <v>2327.8</v>
       </c>
       <c r="K42">
         <v>1</v>
@@ -29644,17 +29644,17 @@
         <v>1.0001</v>
       </c>
       <c r="M42">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="N42">
-        <v>0.0002449518806358951</v>
+        <v>0.0002856212000216427</v>
       </c>
       <c r="O42">
-        <v>0.03625229849217988</v>
+        <v>0.04007699114601319</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>[0.0002, 0.0363]</t>
+          <t>[0.0003, 0.0401]</t>
         </is>
       </c>
     </row>
@@ -29688,35 +29688,35 @@
         </is>
       </c>
       <c r="G43">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="H43">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="I43">
-        <v>1.996910908670789E-05</v>
+        <v>1.30210617703425E-05</v>
       </c>
       <c r="J43">
-        <v>1344.2</v>
+        <v>3318</v>
       </c>
       <c r="K43">
-        <v>1.0016</v>
+        <v>1.0007</v>
       </c>
       <c r="L43">
-        <v>1.0018</v>
+        <v>1.0008</v>
       </c>
       <c r="M43">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="N43">
-        <v>0.1242406376004758</v>
+        <v>0.1242264614416188</v>
       </c>
       <c r="O43">
-        <v>0.1270980490776865</v>
+        <v>0.1271816029686873</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>[0.1242, 0.1271]</t>
+          <t>[0.1242, 0.1272]</t>
         </is>
       </c>
     </row>
@@ -29750,31 +29750,31 @@
         </is>
       </c>
       <c r="G44">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="H44">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="I44">
-        <v>1.683505527229803E-05</v>
+        <v>1.020921344739324E-05</v>
       </c>
       <c r="J44">
-        <v>1041.4</v>
+        <v>2851.2</v>
       </c>
       <c r="K44">
-        <v>1.0008</v>
+        <v>1.0003</v>
       </c>
       <c r="L44">
-        <v>1.0009</v>
+        <v>1.0003</v>
       </c>
       <c r="M44">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="N44">
-        <v>0.06283446095178546</v>
+        <v>0.06283477689587211</v>
       </c>
       <c r="O44">
-        <v>0.06498835543089833</v>
+        <v>0.06500131971690672</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -29812,35 +29812,35 @@
         </is>
       </c>
       <c r="G45">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="H45">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="I45">
-        <v>7.287717726856617E-05</v>
+        <v>4.844680439743285E-05</v>
       </c>
       <c r="J45">
-        <v>1607</v>
+        <v>3850.4</v>
       </c>
       <c r="K45">
-        <v>1.0027</v>
+        <v>1.0002</v>
       </c>
       <c r="L45">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M45">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="N45">
-        <v>0.08530357549931405</v>
+        <v>0.08530411553282874</v>
       </c>
       <c r="O45">
-        <v>0.09676944586807242</v>
+        <v>0.09708120921233582</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>[0.0853, 0.0968]</t>
+          <t>[0.0853, 0.0971]</t>
         </is>
       </c>
     </row>
@@ -29874,31 +29874,31 @@
         </is>
       </c>
       <c r="G46">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="H46">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="I46">
-        <v>3.986943120105059E-05</v>
+        <v>2.631252420617495E-05</v>
       </c>
       <c r="J46">
-        <v>1488.3</v>
+        <v>3549.4</v>
       </c>
       <c r="K46">
-        <v>1.0026</v>
+        <v>1</v>
       </c>
       <c r="L46">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="M46">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="N46">
-        <v>0.04340335790008991</v>
+        <v>0.04337718702816454</v>
       </c>
       <c r="O46">
-        <v>0.04949428357228296</v>
+        <v>0.04953662420187081</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -29936,35 +29936,35 @@
         </is>
       </c>
       <c r="G47">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="H47">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="I47">
-        <v>0.0001029288770320282</v>
+        <v>6.927062815829008E-05</v>
       </c>
       <c r="J47">
-        <v>1613</v>
+        <v>3780.6</v>
       </c>
       <c r="K47">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="L47">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M47">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="N47">
-        <v>0.03999117999120268</v>
+        <v>0.03994847125857982</v>
       </c>
       <c r="O47">
-        <v>0.05616933018720535</v>
+        <v>0.05673759616221472</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>[0.0400, 0.0562]</t>
+          <t>[0.0399, 0.0567]</t>
         </is>
       </c>
     </row>
@@ -29998,35 +29998,35 @@
         </is>
       </c>
       <c r="G48">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="H48">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="I48">
-        <v>5.51738195653668E-05</v>
+        <v>3.693842765066764E-05</v>
       </c>
       <c r="J48">
-        <v>1543.5</v>
+        <v>3616</v>
       </c>
       <c r="K48">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L48">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M48">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="N48">
-        <v>0.02064486387576463</v>
+        <v>0.02057363057052737</v>
       </c>
       <c r="O48">
-        <v>0.02922876830495247</v>
+        <v>0.02929047714320697</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>[0.0206, 0.0292]</t>
+          <t>[0.0206, 0.0293]</t>
         </is>
       </c>
     </row>
@@ -30060,35 +30060,35 @@
         </is>
       </c>
       <c r="G49">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="H49">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="I49">
-        <v>7.654870579497798E-05</v>
+        <v>5.163247376084753E-05</v>
       </c>
       <c r="J49">
-        <v>1618.5</v>
+        <v>3800.1</v>
       </c>
       <c r="K49">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L49">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M49">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="N49">
-        <v>0.01283181136513961</v>
+        <v>0.01279121060028293</v>
       </c>
       <c r="O49">
-        <v>0.02486300206783066</v>
+        <v>0.02534096888804091</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>[0.0128, 0.0249]</t>
+          <t>[0.0128, 0.0253]</t>
         </is>
       </c>
     </row>
@@ -30122,35 +30122,35 @@
         </is>
       </c>
       <c r="G50">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="H50">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="I50">
-        <v>4.173482703340465E-05</v>
+        <v>2.809001079626773E-05</v>
       </c>
       <c r="J50">
-        <v>1549.7</v>
+        <v>3629</v>
       </c>
       <c r="K50">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L50">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M50">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="N50">
-        <v>0.006754465912628241</v>
+        <v>0.006711515300852532</v>
       </c>
       <c r="O50">
-        <v>0.01324374278248805</v>
+        <v>0.01334017469519632</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>[0.0068, 0.0132]</t>
+          <t>[0.0067, 0.0133]</t>
         </is>
       </c>
     </row>
@@ -30184,35 +30184,35 @@
         </is>
       </c>
       <c r="G51">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="H51">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="I51">
-        <v>3.545284751407308E-05</v>
+        <v>2.416065724367434E-05</v>
       </c>
       <c r="J51">
-        <v>1631.4</v>
+        <v>3795.6</v>
       </c>
       <c r="K51">
-        <v>1.0025</v>
+        <v>1.0001</v>
       </c>
       <c r="L51">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="M51">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="N51">
-        <v>0.002821790209533828</v>
+        <v>0.002799332792224822</v>
       </c>
       <c r="O51">
-        <v>0.008395180840575273</v>
+        <v>0.008648722296811141</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>[0.0028, 0.0084]</t>
+          <t>[0.0028, 0.0086]</t>
         </is>
       </c>
     </row>
@@ -30246,35 +30246,35 @@
         </is>
       </c>
       <c r="G52">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="H52">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="I52">
-        <v>1.984959082910289E-05</v>
+        <v>1.348852967546526E-05</v>
       </c>
       <c r="J52">
-        <v>1560.3</v>
+        <v>3641.1</v>
       </c>
       <c r="K52">
-        <v>1.0025</v>
+        <v>1.0001</v>
       </c>
       <c r="L52">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="M52">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="N52">
-        <v>0.001519424188693608</v>
+        <v>0.00150537464286404</v>
       </c>
       <c r="O52">
-        <v>0.004612211856696236</v>
+        <v>0.004672985536810267</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>[0.0015, 0.0046]</t>
+          <t>[0.0015, 0.0047]</t>
         </is>
       </c>
     </row>
@@ -30308,35 +30308,35 @@
         </is>
       </c>
       <c r="G53">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="H53">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="I53">
-        <v>0.0378516379781366</v>
+        <v>0.02550205715002106</v>
       </c>
       <c r="J53">
-        <v>1614.6</v>
+        <v>3787.6</v>
       </c>
       <c r="K53">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L53">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M53">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="N53">
-        <v>31.99254556149809</v>
+        <v>31.94745644144655</v>
       </c>
       <c r="O53">
-        <v>37.93542068119201</v>
+        <v>38.14741835772089</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>[31.9925, 37.9354]</t>
+          <t>[31.9475, 38.1474]</t>
         </is>
       </c>
     </row>
@@ -30370,35 +30370,35 @@
         </is>
       </c>
       <c r="G54">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="H54">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="I54">
-        <v>0.04030004615481509</v>
+        <v>0.02712816536419896</v>
       </c>
       <c r="J54">
-        <v>1551.4</v>
+        <v>3630.6</v>
       </c>
       <c r="K54">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L54">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M54">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="N54">
-        <v>32.24875528724777</v>
+        <v>32.21258652369725</v>
       </c>
       <c r="O54">
-        <v>38.52489088509614</v>
+        <v>38.63563343246012</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>[32.2488, 38.5249]</t>
+          <t>[32.2126, 38.6356]</t>
         </is>
       </c>
     </row>
@@ -30432,35 +30432,35 @@
         </is>
       </c>
       <c r="G55">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="H55">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="I55">
-        <v>0.001085847783755566</v>
+        <v>0.0007306544822292565</v>
       </c>
       <c r="J55">
-        <v>1612.6</v>
+        <v>3778.7</v>
       </c>
       <c r="K55">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="L55">
-        <v>1.0029</v>
+        <v>1.0002</v>
       </c>
       <c r="M55">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="N55">
-        <v>3.465502924459196</v>
+        <v>3.464092567052742</v>
       </c>
       <c r="O55">
-        <v>3.635885258255161</v>
+        <v>3.641458084607688</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>[3.4655, 3.6359]</t>
+          <t>[3.4641, 3.6415]</t>
         </is>
       </c>
     </row>
@@ -30494,31 +30494,31 @@
         </is>
       </c>
       <c r="G56">
-        <v>1.589311306603231</v>
+        <v>1.589395984848507</v>
       </c>
       <c r="H56">
-        <v>0.007205628292603781</v>
+        <v>0.007262318948204624</v>
       </c>
       <c r="I56">
-        <v>0.0002252675616788616</v>
+        <v>0.0001460825366373568</v>
       </c>
       <c r="J56">
-        <v>1023.2</v>
+        <v>2471.5</v>
       </c>
       <c r="K56">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L56">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M56">
-        <v>1.587119633634973</v>
+        <v>1.587220493981195</v>
       </c>
       <c r="N56">
-        <v>1.582167677340778</v>
+        <v>1.582191212529661</v>
       </c>
       <c r="O56">
-        <v>1.608904274809916</v>
+        <v>1.608928520286697</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -30556,35 +30556,35 @@
         </is>
       </c>
       <c r="G57">
-        <v>14087.40902959247</v>
+        <v>14123.64149129999</v>
       </c>
       <c r="H57">
-        <v>1445.727510630541</v>
+        <v>1498.001853014637</v>
       </c>
       <c r="I57">
-        <v>52.71048431542673</v>
+        <v>36.50273536976891</v>
       </c>
       <c r="J57">
-        <v>752.3</v>
+        <v>1684.1</v>
       </c>
       <c r="K57">
-        <v>1.0016</v>
+        <v>1.0007</v>
       </c>
       <c r="L57">
-        <v>1.0018</v>
+        <v>1.0008</v>
       </c>
       <c r="M57">
-        <v>13992.38790436515</v>
+        <v>14004.29100480898</v>
       </c>
       <c r="N57">
-        <v>11588.8616471647</v>
+        <v>11516.91198988923</v>
       </c>
       <c r="O57">
-        <v>17266.52511340762</v>
+        <v>17387.29688123515</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>[11588.8616, 17266.5251]</t>
+          <t>[11516.9120, 17387.2969]</t>
         </is>
       </c>
     </row>
@@ -30618,35 +30618,35 @@
         </is>
       </c>
       <c r="G58">
-        <v>0.3113032558764295</v>
+        <v>0.3232031014683357</v>
       </c>
       <c r="H58">
-        <v>0.1362093634617424</v>
+        <v>0.1420946102486272</v>
       </c>
       <c r="I58">
-        <v>0.007187725811170085</v>
+        <v>0.005248126246874685</v>
       </c>
       <c r="J58">
-        <v>359.1</v>
+        <v>733.1</v>
       </c>
       <c r="K58">
-        <v>1.021</v>
+        <v>1.0073</v>
       </c>
       <c r="L58">
-        <v>1.0212</v>
+        <v>1.0074</v>
       </c>
       <c r="M58">
-        <v>0.316257303341141</v>
+        <v>0.329737376709393</v>
       </c>
       <c r="N58">
-        <v>0.02694270680745655</v>
+        <v>0.02380958686559168</v>
       </c>
       <c r="O58">
-        <v>0.5693657637896794</v>
+        <v>0.5866353602915522</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>[0.0269, 0.5694]</t>
+          <t>[0.0238, 0.5866]</t>
         </is>
       </c>
     </row>
@@ -30680,35 +30680,35 @@
         </is>
       </c>
       <c r="G59">
-        <v>-0.1161112990728373</v>
+        <v>-0.1287407946727498</v>
       </c>
       <c r="H59">
-        <v>0.1148021978489128</v>
+        <v>0.1205661088449834</v>
       </c>
       <c r="I59">
-        <v>0.004777383282242065</v>
+        <v>0.003673175758948686</v>
       </c>
       <c r="J59">
-        <v>577.5</v>
+        <v>1077.4</v>
       </c>
       <c r="K59">
-        <v>1.0004</v>
+        <v>1.0005</v>
       </c>
       <c r="L59">
         <v>1.0006</v>
       </c>
       <c r="M59">
-        <v>-0.1133521931553859</v>
+        <v>-0.1273749279336696</v>
       </c>
       <c r="N59">
-        <v>-0.3386719515336633</v>
+        <v>-0.3651564914560492</v>
       </c>
       <c r="O59">
-        <v>0.1091078866312331</v>
+        <v>0.1069579387757273</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>[-0.3387, 0.1091]</t>
+          <t>[-0.3652, 0.1070]</t>
         </is>
       </c>
     </row>
@@ -30742,35 +30742,35 @@
         </is>
       </c>
       <c r="G60">
-        <v>-0.5116146559729645</v>
+        <v>-0.5369591626463901</v>
       </c>
       <c r="H60">
-        <v>0.1871635112221394</v>
+        <v>0.2036126439218424</v>
       </c>
       <c r="I60">
-        <v>0.01356939193655912</v>
+        <v>0.009715251156275482</v>
       </c>
       <c r="J60">
-        <v>190.2</v>
+        <v>439.2</v>
       </c>
       <c r="K60">
-        <v>1.0055</v>
+        <v>1.005</v>
       </c>
       <c r="L60">
-        <v>1.0057</v>
+        <v>1.005</v>
       </c>
       <c r="M60">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="N60">
-        <v>-0.8514261295155847</v>
+        <v>-0.9272919620447222</v>
       </c>
       <c r="O60">
-        <v>-0.1024529610643907</v>
+        <v>-0.1120617046669647</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>[-0.8514, -0.1025]</t>
+          <t>[-0.9273, -0.1121]</t>
         </is>
       </c>
     </row>
@@ -30804,35 +30804,35 @@
         </is>
       </c>
       <c r="G61">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="H61">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="I61">
-        <v>0.005794357245884296</v>
+        <v>0.004167663529072831</v>
       </c>
       <c r="J61">
-        <v>433.1</v>
+        <v>926.6</v>
       </c>
       <c r="K61">
-        <v>1</v>
+        <v>1.0017</v>
       </c>
       <c r="L61">
-        <v>1.0001</v>
+        <v>1.0017</v>
       </c>
       <c r="M61">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="N61">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="O61">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>[-0.5470, -0.0704]</t>
+          <t>[-0.5529, -0.0508]</t>
         </is>
       </c>
     </row>
@@ -30866,35 +30866,35 @@
         </is>
       </c>
       <c r="G62">
-        <v>-1.666137154963477</v>
+        <v>-1.676201540987581</v>
       </c>
       <c r="H62">
-        <v>1.030182074355619</v>
+        <v>1.035283833008518</v>
       </c>
       <c r="I62">
-        <v>0.100866393262972</v>
+        <v>0.06791265277941498</v>
       </c>
       <c r="J62">
-        <v>104.3</v>
+        <v>232.4</v>
       </c>
       <c r="K62">
-        <v>1.0817</v>
+        <v>1.0198</v>
       </c>
       <c r="L62">
-        <v>1.0819</v>
+        <v>1.0199</v>
       </c>
       <c r="M62">
-        <v>-1.628339858179879</v>
+        <v>-1.675147167474839</v>
       </c>
       <c r="N62">
-        <v>-3.870161755723977</v>
+        <v>-3.805123165114205</v>
       </c>
       <c r="O62">
-        <v>0.1267385224481098</v>
+        <v>0.1771553118029174</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>[-3.8702, 0.1267]</t>
+          <t>[-3.8051, 0.1772]</t>
         </is>
       </c>
     </row>
@@ -30928,35 +30928,35 @@
         </is>
       </c>
       <c r="G63">
-        <v>0.06196936670816747</v>
+        <v>0.06535679301344875</v>
       </c>
       <c r="H63">
-        <v>0.0772600688734436</v>
+        <v>0.07677840040677844</v>
       </c>
       <c r="I63">
-        <v>0.002160805820487455</v>
+        <v>0.001474194024410116</v>
       </c>
       <c r="J63">
-        <v>1278.4</v>
+        <v>2712.5</v>
       </c>
       <c r="K63">
-        <v>1.0072</v>
+        <v>1.0006</v>
       </c>
       <c r="L63">
-        <v>1.0074</v>
+        <v>1.0007</v>
       </c>
       <c r="M63">
-        <v>0.06586546619170625</v>
+        <v>0.0686554630567057</v>
       </c>
       <c r="N63">
-        <v>-0.09540206644877555</v>
+        <v>-0.09582465412121587</v>
       </c>
       <c r="O63">
-        <v>0.2074720015902419</v>
+        <v>0.2083591378841529</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>[-0.0954, 0.2075]</t>
+          <t>[-0.0958, 0.2084]</t>
         </is>
       </c>
     </row>
@@ -30990,16 +30990,16 @@
         </is>
       </c>
       <c r="G64">
-        <v>-0.1046798152858951</v>
+        <v>-0.107017835387122</v>
       </c>
       <c r="H64">
-        <v>0.1301398294968226</v>
+        <v>0.1269459264510429</v>
       </c>
       <c r="I64">
-        <v>0.004153229807695243</v>
+        <v>0.002331311468511136</v>
       </c>
       <c r="J64">
-        <v>981.9</v>
+        <v>2965.1</v>
       </c>
       <c r="K64">
         <v>1</v>
@@ -31008,17 +31008,17 @@
         <v>1.0001</v>
       </c>
       <c r="M64">
-        <v>-0.1004581502557295</v>
+        <v>-0.1023315305345405</v>
       </c>
       <c r="N64">
-        <v>-0.3753464505385751</v>
+        <v>-0.3681489359962021</v>
       </c>
       <c r="O64">
-        <v>0.135475681257319</v>
+        <v>0.1248289554633815</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>[-0.3753, 0.1355]</t>
+          <t>[-0.3681, 0.1248]</t>
         </is>
       </c>
     </row>
@@ -31052,35 +31052,35 @@
         </is>
       </c>
       <c r="G65">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="H65">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="I65">
-        <v>0.02436067252164474</v>
+        <v>0.01616118574776551</v>
       </c>
       <c r="J65">
-        <v>104.3</v>
+        <v>243</v>
       </c>
       <c r="K65">
-        <v>1.0628</v>
+        <v>1.0136</v>
       </c>
       <c r="L65">
-        <v>1.063</v>
+        <v>1.0137</v>
       </c>
       <c r="M65">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="N65">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="O65">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>[-0.0167, 0.9905]</t>
+          <t>[0.0128, 1.0033]</t>
         </is>
       </c>
     </row>
@@ -31114,31 +31114,31 @@
         </is>
       </c>
       <c r="G66">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="H66">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="I66">
-        <v>7.424757282131184E-05</v>
+        <v>4.810704063421389E-05</v>
       </c>
       <c r="J66">
-        <v>1024.3</v>
+        <v>2479</v>
       </c>
       <c r="K66">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L66">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M66">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="N66">
-        <v>0.6577796351508191</v>
+        <v>0.6577717760918227</v>
       </c>
       <c r="O66">
-        <v>0.666602501839997</v>
+        <v>0.6665945953183382</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -31176,31 +31176,31 @@
         </is>
       </c>
       <c r="G67">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="H67">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="I67">
-        <v>7.424757282131176E-05</v>
+        <v>4.810704063421387E-05</v>
       </c>
       <c r="J67">
-        <v>1024.3</v>
+        <v>2479</v>
       </c>
       <c r="K67">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L67">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M67">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="N67">
-        <v>0.333397498160003</v>
+        <v>0.3334054046816618</v>
       </c>
       <c r="O67">
-        <v>0.342220364849181</v>
+        <v>0.3422282239081773</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -31238,35 +31238,35 @@
         </is>
       </c>
       <c r="G68">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="H68">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="I68">
-        <v>0.000338960358430166</v>
+        <v>0.0002197621614077366</v>
       </c>
       <c r="J68">
-        <v>1023.5</v>
+        <v>2473.4</v>
       </c>
       <c r="K68">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L68">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M68">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="N68">
-        <v>1.000288769513282</v>
+        <v>1.000324356132659</v>
       </c>
       <c r="O68">
-        <v>1.040531954963664</v>
+        <v>1.040568283247922</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>[1.0003, 1.0405]</t>
+          <t>[1.0003, 1.0406]</t>
         </is>
       </c>
     </row>
@@ -31300,16 +31300,16 @@
         </is>
       </c>
       <c r="G69">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="H69">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="I69">
-        <v>0.0003294579253450585</v>
+        <v>0.0002222946018841949</v>
       </c>
       <c r="J69">
-        <v>947</v>
+        <v>2327.8</v>
       </c>
       <c r="K69">
         <v>1</v>
@@ -31318,17 +31318,17 @@
         <v>1.0001</v>
       </c>
       <c r="M69">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="N69">
-        <v>0.0002449518806358951</v>
+        <v>0.0002856212000216427</v>
       </c>
       <c r="O69">
-        <v>0.03625229849217988</v>
+        <v>0.04007699114601319</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>[0.0002, 0.0363]</t>
+          <t>[0.0003, 0.0401]</t>
         </is>
       </c>
     </row>
@@ -31362,35 +31362,35 @@
         </is>
       </c>
       <c r="G70">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="H70">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="I70">
-        <v>1.996910908670789E-05</v>
+        <v>1.30210617703425E-05</v>
       </c>
       <c r="J70">
-        <v>1344.2</v>
+        <v>3318</v>
       </c>
       <c r="K70">
-        <v>1.0016</v>
+        <v>1.0007</v>
       </c>
       <c r="L70">
-        <v>1.0018</v>
+        <v>1.0008</v>
       </c>
       <c r="M70">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="N70">
-        <v>0.1242406376004758</v>
+        <v>0.1242264614416188</v>
       </c>
       <c r="O70">
-        <v>0.1270980490776865</v>
+        <v>0.1271816029686873</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>[0.1242, 0.1271]</t>
+          <t>[0.1242, 0.1272]</t>
         </is>
       </c>
     </row>
@@ -31424,31 +31424,31 @@
         </is>
       </c>
       <c r="G71">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="H71">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="I71">
-        <v>1.683505527229803E-05</v>
+        <v>1.020921344739324E-05</v>
       </c>
       <c r="J71">
-        <v>1041.4</v>
+        <v>2851.2</v>
       </c>
       <c r="K71">
-        <v>1.0008</v>
+        <v>1.0003</v>
       </c>
       <c r="L71">
-        <v>1.0009</v>
+        <v>1.0003</v>
       </c>
       <c r="M71">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="N71">
-        <v>0.06283446095178546</v>
+        <v>0.06283477689587211</v>
       </c>
       <c r="O71">
-        <v>0.06498835543089833</v>
+        <v>0.06500131971690672</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -31486,35 +31486,35 @@
         </is>
       </c>
       <c r="G72">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="H72">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="I72">
-        <v>7.287717726856617E-05</v>
+        <v>4.844680439743285E-05</v>
       </c>
       <c r="J72">
-        <v>1607</v>
+        <v>3850.4</v>
       </c>
       <c r="K72">
-        <v>1.0027</v>
+        <v>1.0002</v>
       </c>
       <c r="L72">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M72">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="N72">
-        <v>0.08530357549931405</v>
+        <v>0.08530411553282874</v>
       </c>
       <c r="O72">
-        <v>0.09676944586807242</v>
+        <v>0.09708120921233582</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>[0.0853, 0.0968]</t>
+          <t>[0.0853, 0.0971]</t>
         </is>
       </c>
     </row>
@@ -31548,31 +31548,31 @@
         </is>
       </c>
       <c r="G73">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="H73">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="I73">
-        <v>3.986943120105059E-05</v>
+        <v>2.631252420617495E-05</v>
       </c>
       <c r="J73">
-        <v>1488.3</v>
+        <v>3549.4</v>
       </c>
       <c r="K73">
-        <v>1.0026</v>
+        <v>1</v>
       </c>
       <c r="L73">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="M73">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="N73">
-        <v>0.04340335790008991</v>
+        <v>0.04337718702816454</v>
       </c>
       <c r="O73">
-        <v>0.04949428357228296</v>
+        <v>0.04953662420187081</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -31610,35 +31610,35 @@
         </is>
       </c>
       <c r="G74">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="H74">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="I74">
-        <v>0.0001029288770320282</v>
+        <v>6.927062815829008E-05</v>
       </c>
       <c r="J74">
-        <v>1613</v>
+        <v>3780.6</v>
       </c>
       <c r="K74">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="L74">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M74">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="N74">
-        <v>0.03999117999120268</v>
+        <v>0.03994847125857982</v>
       </c>
       <c r="O74">
-        <v>0.05616933018720535</v>
+        <v>0.05673759616221472</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>[0.0400, 0.0562]</t>
+          <t>[0.0399, 0.0567]</t>
         </is>
       </c>
     </row>
@@ -31672,35 +31672,35 @@
         </is>
       </c>
       <c r="G75">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="H75">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="I75">
-        <v>5.51738195653668E-05</v>
+        <v>3.693842765066764E-05</v>
       </c>
       <c r="J75">
-        <v>1543.5</v>
+        <v>3616</v>
       </c>
       <c r="K75">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L75">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M75">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="N75">
-        <v>0.02064486387576463</v>
+        <v>0.02057363057052737</v>
       </c>
       <c r="O75">
-        <v>0.02922876830495247</v>
+        <v>0.02929047714320697</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>[0.0206, 0.0292]</t>
+          <t>[0.0206, 0.0293]</t>
         </is>
       </c>
     </row>
@@ -31734,35 +31734,35 @@
         </is>
       </c>
       <c r="G76">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="H76">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="I76">
-        <v>7.654870579497798E-05</v>
+        <v>5.163247376084753E-05</v>
       </c>
       <c r="J76">
-        <v>1618.5</v>
+        <v>3800.1</v>
       </c>
       <c r="K76">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L76">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M76">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="N76">
-        <v>0.01283181136513961</v>
+        <v>0.01279121060028293</v>
       </c>
       <c r="O76">
-        <v>0.02486300206783066</v>
+        <v>0.02534096888804091</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>[0.0128, 0.0249]</t>
+          <t>[0.0128, 0.0253]</t>
         </is>
       </c>
     </row>
@@ -31796,35 +31796,35 @@
         </is>
       </c>
       <c r="G77">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="H77">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="I77">
-        <v>4.173482703340465E-05</v>
+        <v>2.809001079626773E-05</v>
       </c>
       <c r="J77">
-        <v>1549.7</v>
+        <v>3629</v>
       </c>
       <c r="K77">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L77">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M77">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="N77">
-        <v>0.006754465912628241</v>
+        <v>0.006711515300852532</v>
       </c>
       <c r="O77">
-        <v>0.01324374278248805</v>
+        <v>0.01334017469519632</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[0.0068, 0.0132]</t>
+          <t>[0.0067, 0.0133]</t>
         </is>
       </c>
     </row>
@@ -31858,35 +31858,35 @@
         </is>
       </c>
       <c r="G78">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="H78">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="I78">
-        <v>3.545284751407308E-05</v>
+        <v>2.416065724367434E-05</v>
       </c>
       <c r="J78">
-        <v>1631.4</v>
+        <v>3795.6</v>
       </c>
       <c r="K78">
-        <v>1.0025</v>
+        <v>1.0001</v>
       </c>
       <c r="L78">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="M78">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="N78">
-        <v>0.002821790209533828</v>
+        <v>0.002799332792224822</v>
       </c>
       <c r="O78">
-        <v>0.008395180840575273</v>
+        <v>0.008648722296811141</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[0.0028, 0.0084]</t>
+          <t>[0.0028, 0.0086]</t>
         </is>
       </c>
     </row>
@@ -31920,35 +31920,35 @@
         </is>
       </c>
       <c r="G79">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="H79">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="I79">
-        <v>1.984959082910289E-05</v>
+        <v>1.348852967546526E-05</v>
       </c>
       <c r="J79">
-        <v>1560.3</v>
+        <v>3641.1</v>
       </c>
       <c r="K79">
-        <v>1.0025</v>
+        <v>1.0001</v>
       </c>
       <c r="L79">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="M79">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="N79">
-        <v>0.001519424188693608</v>
+        <v>0.00150537464286404</v>
       </c>
       <c r="O79">
-        <v>0.004612211856696236</v>
+        <v>0.004672985536810267</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>[0.0015, 0.0046]</t>
+          <t>[0.0015, 0.0047]</t>
         </is>
       </c>
     </row>
@@ -31982,35 +31982,35 @@
         </is>
       </c>
       <c r="G80">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="H80">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="I80">
-        <v>0.0378516379781366</v>
+        <v>0.02550205715002106</v>
       </c>
       <c r="J80">
-        <v>1614.6</v>
+        <v>3787.6</v>
       </c>
       <c r="K80">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L80">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M80">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="N80">
-        <v>31.99254556149809</v>
+        <v>31.94745644144655</v>
       </c>
       <c r="O80">
-        <v>37.93542068119201</v>
+        <v>38.14741835772089</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>[31.9925, 37.9354]</t>
+          <t>[31.9475, 38.1474]</t>
         </is>
       </c>
     </row>
@@ -32044,35 +32044,35 @@
         </is>
       </c>
       <c r="G81">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="H81">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="I81">
-        <v>0.04030004615481509</v>
+        <v>0.02712816536419896</v>
       </c>
       <c r="J81">
-        <v>1551.4</v>
+        <v>3630.6</v>
       </c>
       <c r="K81">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L81">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M81">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="N81">
-        <v>32.24875528724777</v>
+        <v>32.21258652369725</v>
       </c>
       <c r="O81">
-        <v>38.52489088509614</v>
+        <v>38.63563343246012</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>[32.2488, 38.5249]</t>
+          <t>[32.2126, 38.6356]</t>
         </is>
       </c>
     </row>
@@ -32106,35 +32106,35 @@
         </is>
       </c>
       <c r="G82">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="H82">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="I82">
-        <v>0.001085847783755566</v>
+        <v>0.0007306544822292565</v>
       </c>
       <c r="J82">
-        <v>1612.6</v>
+        <v>3778.7</v>
       </c>
       <c r="K82">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="L82">
-        <v>1.0029</v>
+        <v>1.0002</v>
       </c>
       <c r="M82">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="N82">
-        <v>3.465502924459196</v>
+        <v>3.464092567052742</v>
       </c>
       <c r="O82">
-        <v>3.635885258255161</v>
+        <v>3.641458084607688</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>[3.4655, 3.6359]</t>
+          <t>[3.4641, 3.6415]</t>
         </is>
       </c>
     </row>
@@ -32168,31 +32168,31 @@
         </is>
       </c>
       <c r="G83">
-        <v>1.589311306603231</v>
+        <v>1.589395984848507</v>
       </c>
       <c r="H83">
-        <v>0.007205628292603781</v>
+        <v>0.007262318948204624</v>
       </c>
       <c r="I83">
-        <v>0.0002252675616788616</v>
+        <v>0.0001460825366373568</v>
       </c>
       <c r="J83">
-        <v>1023.2</v>
+        <v>2471.5</v>
       </c>
       <c r="K83">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L83">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M83">
-        <v>1.587119633634973</v>
+        <v>1.587220493981195</v>
       </c>
       <c r="N83">
-        <v>1.582167677340778</v>
+        <v>1.582191212529661</v>
       </c>
       <c r="O83">
-        <v>1.608904274809916</v>
+        <v>1.608928520286697</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -32230,35 +32230,35 @@
         </is>
       </c>
       <c r="G84">
-        <v>14087.40902959247</v>
+        <v>14123.64149129999</v>
       </c>
       <c r="H84">
-        <v>1445.727510630541</v>
+        <v>1498.001853014637</v>
       </c>
       <c r="I84">
-        <v>52.71048431542673</v>
+        <v>36.50273536976891</v>
       </c>
       <c r="J84">
-        <v>752.3</v>
+        <v>1684.1</v>
       </c>
       <c r="K84">
-        <v>1.0016</v>
+        <v>1.0007</v>
       </c>
       <c r="L84">
-        <v>1.0018</v>
+        <v>1.0008</v>
       </c>
       <c r="M84">
-        <v>13992.38790436515</v>
+        <v>14004.29100480898</v>
       </c>
       <c r="N84">
-        <v>11588.8616471647</v>
+        <v>11516.91198988923</v>
       </c>
       <c r="O84">
-        <v>17266.52511340762</v>
+        <v>17387.29688123515</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>[11588.8616, 17266.5251]</t>
+          <t>[11516.9120, 17387.2969]</t>
         </is>
       </c>
     </row>
@@ -32292,35 +32292,35 @@
         </is>
       </c>
       <c r="G85">
-        <v>0.3113032558764295</v>
+        <v>0.3232031014683357</v>
       </c>
       <c r="H85">
-        <v>0.1362093634617424</v>
+        <v>0.1420946102486272</v>
       </c>
       <c r="I85">
-        <v>0.007187725811170085</v>
+        <v>0.005248126246874685</v>
       </c>
       <c r="J85">
-        <v>359.1</v>
+        <v>733.1</v>
       </c>
       <c r="K85">
-        <v>1.021</v>
+        <v>1.0073</v>
       </c>
       <c r="L85">
-        <v>1.0212</v>
+        <v>1.0074</v>
       </c>
       <c r="M85">
-        <v>0.316257303341141</v>
+        <v>0.329737376709393</v>
       </c>
       <c r="N85">
-        <v>0.02694270680745655</v>
+        <v>0.02380958686559168</v>
       </c>
       <c r="O85">
-        <v>0.5693657637896794</v>
+        <v>0.5866353602915522</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>[0.0269, 0.5694]</t>
+          <t>[0.0238, 0.5866]</t>
         </is>
       </c>
     </row>
@@ -32354,35 +32354,35 @@
         </is>
       </c>
       <c r="G86">
-        <v>-0.1161112990728373</v>
+        <v>-0.1287407946727498</v>
       </c>
       <c r="H86">
-        <v>0.1148021978489128</v>
+        <v>0.1205661088449834</v>
       </c>
       <c r="I86">
-        <v>0.004777383282242065</v>
+        <v>0.003673175758948686</v>
       </c>
       <c r="J86">
-        <v>577.5</v>
+        <v>1077.4</v>
       </c>
       <c r="K86">
-        <v>1.0004</v>
+        <v>1.0005</v>
       </c>
       <c r="L86">
         <v>1.0006</v>
       </c>
       <c r="M86">
-        <v>-0.1133521931553859</v>
+        <v>-0.1273749279336696</v>
       </c>
       <c r="N86">
-        <v>-0.3386719515336633</v>
+        <v>-0.3651564914560492</v>
       </c>
       <c r="O86">
-        <v>0.1091078866312331</v>
+        <v>0.1069579387757273</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>[-0.3387, 0.1091]</t>
+          <t>[-0.3652, 0.1070]</t>
         </is>
       </c>
     </row>
@@ -32416,35 +32416,35 @@
         </is>
       </c>
       <c r="G87">
-        <v>-0.5116146559729645</v>
+        <v>-0.5369591626463901</v>
       </c>
       <c r="H87">
-        <v>0.1871635112221394</v>
+        <v>0.2036126439218424</v>
       </c>
       <c r="I87">
-        <v>0.01356939193655912</v>
+        <v>0.009715251156275482</v>
       </c>
       <c r="J87">
-        <v>190.2</v>
+        <v>439.2</v>
       </c>
       <c r="K87">
-        <v>1.0055</v>
+        <v>1.005</v>
       </c>
       <c r="L87">
-        <v>1.0057</v>
+        <v>1.005</v>
       </c>
       <c r="M87">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="N87">
-        <v>-0.8514261295155847</v>
+        <v>-0.9272919620447222</v>
       </c>
       <c r="O87">
-        <v>-0.1024529610643907</v>
+        <v>-0.1120617046669647</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>[-0.8514, -0.1025]</t>
+          <t>[-0.9273, -0.1121]</t>
         </is>
       </c>
     </row>
@@ -32478,35 +32478,35 @@
         </is>
       </c>
       <c r="G88">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="H88">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="I88">
-        <v>0.005794357245884296</v>
+        <v>0.004167663529072831</v>
       </c>
       <c r="J88">
-        <v>433.1</v>
+        <v>926.6</v>
       </c>
       <c r="K88">
-        <v>1</v>
+        <v>1.0017</v>
       </c>
       <c r="L88">
-        <v>1.0001</v>
+        <v>1.0017</v>
       </c>
       <c r="M88">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="N88">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="O88">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>[-0.5470, -0.0704]</t>
+          <t>[-0.5529, -0.0508]</t>
         </is>
       </c>
     </row>
@@ -32540,35 +32540,35 @@
         </is>
       </c>
       <c r="G89">
-        <v>-1.666137154963477</v>
+        <v>-1.676201540987581</v>
       </c>
       <c r="H89">
-        <v>1.030182074355619</v>
+        <v>1.035283833008518</v>
       </c>
       <c r="I89">
-        <v>0.100866393262972</v>
+        <v>0.06791265277941498</v>
       </c>
       <c r="J89">
-        <v>104.3</v>
+        <v>232.4</v>
       </c>
       <c r="K89">
-        <v>1.0817</v>
+        <v>1.0198</v>
       </c>
       <c r="L89">
-        <v>1.0819</v>
+        <v>1.0199</v>
       </c>
       <c r="M89">
-        <v>-1.628339858179879</v>
+        <v>-1.675147167474839</v>
       </c>
       <c r="N89">
-        <v>-3.870161755723977</v>
+        <v>-3.805123165114205</v>
       </c>
       <c r="O89">
-        <v>0.1267385224481098</v>
+        <v>0.1771553118029174</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>[-3.8702, 0.1267]</t>
+          <t>[-3.8051, 0.1772]</t>
         </is>
       </c>
     </row>
@@ -32602,35 +32602,35 @@
         </is>
       </c>
       <c r="G90">
-        <v>0.06196936670816747</v>
+        <v>0.06535679301344875</v>
       </c>
       <c r="H90">
-        <v>0.0772600688734436</v>
+        <v>0.07677840040677844</v>
       </c>
       <c r="I90">
-        <v>0.002160805820487455</v>
+        <v>0.001474194024410116</v>
       </c>
       <c r="J90">
-        <v>1278.4</v>
+        <v>2712.5</v>
       </c>
       <c r="K90">
-        <v>1.0072</v>
+        <v>1.0006</v>
       </c>
       <c r="L90">
-        <v>1.0074</v>
+        <v>1.0007</v>
       </c>
       <c r="M90">
-        <v>0.06586546619170625</v>
+        <v>0.0686554630567057</v>
       </c>
       <c r="N90">
-        <v>-0.09540206644877555</v>
+        <v>-0.09582465412121587</v>
       </c>
       <c r="O90">
-        <v>0.2074720015902419</v>
+        <v>0.2083591378841529</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>[-0.0954, 0.2075]</t>
+          <t>[-0.0958, 0.2084]</t>
         </is>
       </c>
     </row>
@@ -32664,16 +32664,16 @@
         </is>
       </c>
       <c r="G91">
-        <v>-0.1046798152858951</v>
+        <v>-0.107017835387122</v>
       </c>
       <c r="H91">
-        <v>0.1301398294968226</v>
+        <v>0.1269459264510429</v>
       </c>
       <c r="I91">
-        <v>0.004153229807695243</v>
+        <v>0.002331311468511136</v>
       </c>
       <c r="J91">
-        <v>981.9</v>
+        <v>2965.1</v>
       </c>
       <c r="K91">
         <v>1</v>
@@ -32682,17 +32682,17 @@
         <v>1.0001</v>
       </c>
       <c r="M91">
-        <v>-0.1004581502557295</v>
+        <v>-0.1023315305345405</v>
       </c>
       <c r="N91">
-        <v>-0.3753464505385751</v>
+        <v>-0.3681489359962021</v>
       </c>
       <c r="O91">
-        <v>0.135475681257319</v>
+        <v>0.1248289554633815</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>[-0.3753, 0.1355]</t>
+          <t>[-0.3681, 0.1248]</t>
         </is>
       </c>
     </row>
@@ -32726,35 +32726,35 @@
         </is>
       </c>
       <c r="G92">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="H92">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="I92">
-        <v>0.02436067252164474</v>
+        <v>0.01616118574776551</v>
       </c>
       <c r="J92">
-        <v>104.3</v>
+        <v>243</v>
       </c>
       <c r="K92">
-        <v>1.0628</v>
+        <v>1.0136</v>
       </c>
       <c r="L92">
-        <v>1.063</v>
+        <v>1.0137</v>
       </c>
       <c r="M92">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="N92">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="O92">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>[-0.0167, 0.9905]</t>
+          <t>[0.0128, 1.0033]</t>
         </is>
       </c>
     </row>
@@ -32788,31 +32788,31 @@
         </is>
       </c>
       <c r="G93">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="H93">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="I93">
-        <v>7.424757282131184E-05</v>
+        <v>4.810704063421389E-05</v>
       </c>
       <c r="J93">
-        <v>1024.3</v>
+        <v>2479</v>
       </c>
       <c r="K93">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L93">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M93">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="N93">
-        <v>0.6577796351508191</v>
+        <v>0.6577717760918227</v>
       </c>
       <c r="O93">
-        <v>0.666602501839997</v>
+        <v>0.6665945953183382</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
@@ -32850,31 +32850,31 @@
         </is>
       </c>
       <c r="G94">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="H94">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="I94">
-        <v>7.424757282131176E-05</v>
+        <v>4.810704063421387E-05</v>
       </c>
       <c r="J94">
-        <v>1024.3</v>
+        <v>2479</v>
       </c>
       <c r="K94">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L94">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M94">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="N94">
-        <v>0.333397498160003</v>
+        <v>0.3334054046816618</v>
       </c>
       <c r="O94">
-        <v>0.342220364849181</v>
+        <v>0.3422282239081773</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
@@ -32912,35 +32912,35 @@
         </is>
       </c>
       <c r="G95">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="H95">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="I95">
-        <v>0.000338960358430166</v>
+        <v>0.0002197621614077366</v>
       </c>
       <c r="J95">
-        <v>1023.5</v>
+        <v>2473.4</v>
       </c>
       <c r="K95">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L95">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M95">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="N95">
-        <v>1.000288769513282</v>
+        <v>1.000324356132659</v>
       </c>
       <c r="O95">
-        <v>1.040531954963664</v>
+        <v>1.040568283247922</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>[1.0003, 1.0405]</t>
+          <t>[1.0003, 1.0406]</t>
         </is>
       </c>
     </row>
@@ -32974,16 +32974,16 @@
         </is>
       </c>
       <c r="G96">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="H96">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="I96">
-        <v>0.0003294579253450585</v>
+        <v>0.0002222946018841949</v>
       </c>
       <c r="J96">
-        <v>947</v>
+        <v>2327.8</v>
       </c>
       <c r="K96">
         <v>1</v>
@@ -32992,17 +32992,17 @@
         <v>1.0001</v>
       </c>
       <c r="M96">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="N96">
-        <v>0.0002449518806358951</v>
+        <v>0.0002856212000216427</v>
       </c>
       <c r="O96">
-        <v>0.03625229849217988</v>
+        <v>0.04007699114601319</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>[0.0002, 0.0363]</t>
+          <t>[0.0003, 0.0401]</t>
         </is>
       </c>
     </row>
@@ -33036,35 +33036,35 @@
         </is>
       </c>
       <c r="G97">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="H97">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="I97">
-        <v>1.996910908670789E-05</v>
+        <v>1.30210617703425E-05</v>
       </c>
       <c r="J97">
-        <v>1344.2</v>
+        <v>3318</v>
       </c>
       <c r="K97">
-        <v>1.0016</v>
+        <v>1.0007</v>
       </c>
       <c r="L97">
-        <v>1.0018</v>
+        <v>1.0008</v>
       </c>
       <c r="M97">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="N97">
-        <v>0.1242406376004758</v>
+        <v>0.1242264614416188</v>
       </c>
       <c r="O97">
-        <v>0.1270980490776865</v>
+        <v>0.1271816029686873</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>[0.1242, 0.1271]</t>
+          <t>[0.1242, 0.1272]</t>
         </is>
       </c>
     </row>
@@ -33098,31 +33098,31 @@
         </is>
       </c>
       <c r="G98">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="H98">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="I98">
-        <v>1.683505527229803E-05</v>
+        <v>1.020921344739324E-05</v>
       </c>
       <c r="J98">
-        <v>1041.4</v>
+        <v>2851.2</v>
       </c>
       <c r="K98">
-        <v>1.0008</v>
+        <v>1.0003</v>
       </c>
       <c r="L98">
-        <v>1.0009</v>
+        <v>1.0003</v>
       </c>
       <c r="M98">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="N98">
-        <v>0.06283446095178546</v>
+        <v>0.06283477689587211</v>
       </c>
       <c r="O98">
-        <v>0.06498835543089833</v>
+        <v>0.06500131971690672</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
@@ -33160,35 +33160,35 @@
         </is>
       </c>
       <c r="G99">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="H99">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="I99">
-        <v>7.287717726856617E-05</v>
+        <v>4.844680439743285E-05</v>
       </c>
       <c r="J99">
-        <v>1607</v>
+        <v>3850.4</v>
       </c>
       <c r="K99">
-        <v>1.0027</v>
+        <v>1.0002</v>
       </c>
       <c r="L99">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M99">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="N99">
-        <v>0.08530357549931405</v>
+        <v>0.08530411553282874</v>
       </c>
       <c r="O99">
-        <v>0.09676944586807242</v>
+        <v>0.09708120921233582</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>[0.0853, 0.0968]</t>
+          <t>[0.0853, 0.0971]</t>
         </is>
       </c>
     </row>
@@ -33222,31 +33222,31 @@
         </is>
       </c>
       <c r="G100">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="H100">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="I100">
-        <v>3.986943120105059E-05</v>
+        <v>2.631252420617495E-05</v>
       </c>
       <c r="J100">
-        <v>1488.3</v>
+        <v>3549.4</v>
       </c>
       <c r="K100">
-        <v>1.0026</v>
+        <v>1</v>
       </c>
       <c r="L100">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="M100">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="N100">
-        <v>0.04340335790008991</v>
+        <v>0.04337718702816454</v>
       </c>
       <c r="O100">
-        <v>0.04949428357228296</v>
+        <v>0.04953662420187081</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -33284,35 +33284,35 @@
         </is>
       </c>
       <c r="G101">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="H101">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="I101">
-        <v>0.0001029288770320282</v>
+        <v>6.927062815829008E-05</v>
       </c>
       <c r="J101">
-        <v>1613</v>
+        <v>3780.6</v>
       </c>
       <c r="K101">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="L101">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M101">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="N101">
-        <v>0.03999117999120268</v>
+        <v>0.03994847125857982</v>
       </c>
       <c r="O101">
-        <v>0.05616933018720535</v>
+        <v>0.05673759616221472</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>[0.0400, 0.0562]</t>
+          <t>[0.0399, 0.0567]</t>
         </is>
       </c>
     </row>
@@ -33346,35 +33346,35 @@
         </is>
       </c>
       <c r="G102">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="H102">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="I102">
-        <v>5.51738195653668E-05</v>
+        <v>3.693842765066764E-05</v>
       </c>
       <c r="J102">
-        <v>1543.5</v>
+        <v>3616</v>
       </c>
       <c r="K102">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L102">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M102">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="N102">
-        <v>0.02064486387576463</v>
+        <v>0.02057363057052737</v>
       </c>
       <c r="O102">
-        <v>0.02922876830495247</v>
+        <v>0.02929047714320697</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>[0.0206, 0.0292]</t>
+          <t>[0.0206, 0.0293]</t>
         </is>
       </c>
     </row>
@@ -33408,35 +33408,35 @@
         </is>
       </c>
       <c r="G103">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="H103">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="I103">
-        <v>7.654870579497798E-05</v>
+        <v>5.163247376084753E-05</v>
       </c>
       <c r="J103">
-        <v>1618.5</v>
+        <v>3800.1</v>
       </c>
       <c r="K103">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L103">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M103">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="N103">
-        <v>0.01283181136513961</v>
+        <v>0.01279121060028293</v>
       </c>
       <c r="O103">
-        <v>0.02486300206783066</v>
+        <v>0.02534096888804091</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>[0.0128, 0.0249]</t>
+          <t>[0.0128, 0.0253]</t>
         </is>
       </c>
     </row>
@@ -33470,35 +33470,35 @@
         </is>
       </c>
       <c r="G104">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="H104">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="I104">
-        <v>4.173482703340465E-05</v>
+        <v>2.809001079626773E-05</v>
       </c>
       <c r="J104">
-        <v>1549.7</v>
+        <v>3629</v>
       </c>
       <c r="K104">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L104">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M104">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="N104">
-        <v>0.006754465912628241</v>
+        <v>0.006711515300852532</v>
       </c>
       <c r="O104">
-        <v>0.01324374278248805</v>
+        <v>0.01334017469519632</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>[0.0068, 0.0132]</t>
+          <t>[0.0067, 0.0133]</t>
         </is>
       </c>
     </row>
@@ -33532,35 +33532,35 @@
         </is>
       </c>
       <c r="G105">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="H105">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="I105">
-        <v>3.545284751407308E-05</v>
+        <v>2.416065724367434E-05</v>
       </c>
       <c r="J105">
-        <v>1631.4</v>
+        <v>3795.6</v>
       </c>
       <c r="K105">
-        <v>1.0025</v>
+        <v>1.0001</v>
       </c>
       <c r="L105">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="M105">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="N105">
-        <v>0.002821790209533828</v>
+        <v>0.002799332792224822</v>
       </c>
       <c r="O105">
-        <v>0.008395180840575273</v>
+        <v>0.008648722296811141</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>[0.0028, 0.0084]</t>
+          <t>[0.0028, 0.0086]</t>
         </is>
       </c>
     </row>
@@ -33594,35 +33594,35 @@
         </is>
       </c>
       <c r="G106">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="H106">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="I106">
-        <v>1.984959082910289E-05</v>
+        <v>1.348852967546526E-05</v>
       </c>
       <c r="J106">
-        <v>1560.3</v>
+        <v>3641.1</v>
       </c>
       <c r="K106">
-        <v>1.0025</v>
+        <v>1.0001</v>
       </c>
       <c r="L106">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="M106">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="N106">
-        <v>0.001519424188693608</v>
+        <v>0.00150537464286404</v>
       </c>
       <c r="O106">
-        <v>0.004612211856696236</v>
+        <v>0.004672985536810267</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>[0.0015, 0.0046]</t>
+          <t>[0.0015, 0.0047]</t>
         </is>
       </c>
     </row>
@@ -33656,35 +33656,35 @@
         </is>
       </c>
       <c r="G107">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="H107">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="I107">
-        <v>0.0378516379781366</v>
+        <v>0.02550205715002106</v>
       </c>
       <c r="J107">
-        <v>1614.6</v>
+        <v>3787.6</v>
       </c>
       <c r="K107">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L107">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M107">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="N107">
-        <v>31.99254556149809</v>
+        <v>31.94745644144655</v>
       </c>
       <c r="O107">
-        <v>37.93542068119201</v>
+        <v>38.14741835772089</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>[31.9925, 37.9354]</t>
+          <t>[31.9475, 38.1474]</t>
         </is>
       </c>
     </row>
@@ -33718,35 +33718,35 @@
         </is>
       </c>
       <c r="G108">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="H108">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="I108">
-        <v>0.04030004615481509</v>
+        <v>0.02712816536419896</v>
       </c>
       <c r="J108">
-        <v>1551.4</v>
+        <v>3630.6</v>
       </c>
       <c r="K108">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L108">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M108">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="N108">
-        <v>32.24875528724777</v>
+        <v>32.21258652369725</v>
       </c>
       <c r="O108">
-        <v>38.52489088509614</v>
+        <v>38.63563343246012</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>[32.2488, 38.5249]</t>
+          <t>[32.2126, 38.6356]</t>
         </is>
       </c>
     </row>
@@ -33780,35 +33780,35 @@
         </is>
       </c>
       <c r="G109">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="H109">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="I109">
-        <v>0.001085847783755566</v>
+        <v>0.0007306544822292565</v>
       </c>
       <c r="J109">
-        <v>1612.6</v>
+        <v>3778.7</v>
       </c>
       <c r="K109">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="L109">
-        <v>1.0029</v>
+        <v>1.0002</v>
       </c>
       <c r="M109">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="N109">
-        <v>3.465502924459196</v>
+        <v>3.464092567052742</v>
       </c>
       <c r="O109">
-        <v>3.635885258255161</v>
+        <v>3.641458084607688</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>[3.4655, 3.6359]</t>
+          <t>[3.4641, 3.6415]</t>
         </is>
       </c>
     </row>
@@ -33842,31 +33842,31 @@
         </is>
       </c>
       <c r="G110">
-        <v>1.589311306603231</v>
+        <v>1.589395984848507</v>
       </c>
       <c r="H110">
-        <v>0.007205628292603781</v>
+        <v>0.007262318948204624</v>
       </c>
       <c r="I110">
-        <v>0.0002252675616788616</v>
+        <v>0.0001460825366373568</v>
       </c>
       <c r="J110">
-        <v>1023.2</v>
+        <v>2471.5</v>
       </c>
       <c r="K110">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L110">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M110">
-        <v>1.587119633634973</v>
+        <v>1.587220493981195</v>
       </c>
       <c r="N110">
-        <v>1.582167677340778</v>
+        <v>1.582191212529661</v>
       </c>
       <c r="O110">
-        <v>1.608904274809916</v>
+        <v>1.608928520286697</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
@@ -33904,35 +33904,35 @@
         </is>
       </c>
       <c r="G111">
-        <v>14087.40902959247</v>
+        <v>14123.64149129999</v>
       </c>
       <c r="H111">
-        <v>1445.727510630541</v>
+        <v>1498.001853014637</v>
       </c>
       <c r="I111">
-        <v>52.71048431542673</v>
+        <v>36.50273536976891</v>
       </c>
       <c r="J111">
-        <v>752.3</v>
+        <v>1684.1</v>
       </c>
       <c r="K111">
-        <v>1.0016</v>
+        <v>1.0007</v>
       </c>
       <c r="L111">
-        <v>1.0018</v>
+        <v>1.0008</v>
       </c>
       <c r="M111">
-        <v>13992.38790436515</v>
+        <v>14004.29100480898</v>
       </c>
       <c r="N111">
-        <v>11588.8616471647</v>
+        <v>11516.91198988923</v>
       </c>
       <c r="O111">
-        <v>17266.52511340762</v>
+        <v>17387.29688123515</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>[11588.8616, 17266.5251]</t>
+          <t>[11516.9120, 17387.2969]</t>
         </is>
       </c>
     </row>
@@ -33966,35 +33966,35 @@
         </is>
       </c>
       <c r="G112">
-        <v>0.3113032558764295</v>
+        <v>0.3232031014683357</v>
       </c>
       <c r="H112">
-        <v>0.1362093634617424</v>
+        <v>0.1420946102486272</v>
       </c>
       <c r="I112">
-        <v>0.007187725811170085</v>
+        <v>0.005248126246874685</v>
       </c>
       <c r="J112">
-        <v>359.1</v>
+        <v>733.1</v>
       </c>
       <c r="K112">
-        <v>1.021</v>
+        <v>1.0073</v>
       </c>
       <c r="L112">
-        <v>1.0212</v>
+        <v>1.0074</v>
       </c>
       <c r="M112">
-        <v>0.316257303341141</v>
+        <v>0.329737376709393</v>
       </c>
       <c r="N112">
-        <v>0.02694270680745655</v>
+        <v>0.02380958686559168</v>
       </c>
       <c r="O112">
-        <v>0.5693657637896794</v>
+        <v>0.5866353602915522</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>[0.0269, 0.5694]</t>
+          <t>[0.0238, 0.5866]</t>
         </is>
       </c>
     </row>
@@ -34028,35 +34028,35 @@
         </is>
       </c>
       <c r="G113">
-        <v>-0.1161112990728373</v>
+        <v>-0.1287407946727498</v>
       </c>
       <c r="H113">
-        <v>0.1148021978489128</v>
+        <v>0.1205661088449834</v>
       </c>
       <c r="I113">
-        <v>0.004777383282242065</v>
+        <v>0.003673175758948686</v>
       </c>
       <c r="J113">
-        <v>577.5</v>
+        <v>1077.4</v>
       </c>
       <c r="K113">
-        <v>1.0004</v>
+        <v>1.0005</v>
       </c>
       <c r="L113">
         <v>1.0006</v>
       </c>
       <c r="M113">
-        <v>-0.1133521931553859</v>
+        <v>-0.1273749279336696</v>
       </c>
       <c r="N113">
-        <v>-0.3386719515336633</v>
+        <v>-0.3651564914560492</v>
       </c>
       <c r="O113">
-        <v>0.1091078866312331</v>
+        <v>0.1069579387757273</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>[-0.3387, 0.1091]</t>
+          <t>[-0.3652, 0.1070]</t>
         </is>
       </c>
     </row>
@@ -34090,35 +34090,35 @@
         </is>
       </c>
       <c r="G114">
-        <v>-0.5116146559729645</v>
+        <v>-0.5369591626463901</v>
       </c>
       <c r="H114">
-        <v>0.1871635112221394</v>
+        <v>0.2036126439218424</v>
       </c>
       <c r="I114">
-        <v>0.01356939193655912</v>
+        <v>0.009715251156275482</v>
       </c>
       <c r="J114">
-        <v>190.2</v>
+        <v>439.2</v>
       </c>
       <c r="K114">
-        <v>1.0055</v>
+        <v>1.005</v>
       </c>
       <c r="L114">
-        <v>1.0057</v>
+        <v>1.005</v>
       </c>
       <c r="M114">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="N114">
-        <v>-0.8514261295155847</v>
+        <v>-0.9272919620447222</v>
       </c>
       <c r="O114">
-        <v>-0.1024529610643907</v>
+        <v>-0.1120617046669647</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>[-0.8514, -0.1025]</t>
+          <t>[-0.9273, -0.1121]</t>
         </is>
       </c>
     </row>
@@ -34152,35 +34152,35 @@
         </is>
       </c>
       <c r="G115">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="H115">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="I115">
-        <v>0.005794357245884296</v>
+        <v>0.004167663529072831</v>
       </c>
       <c r="J115">
-        <v>433.1</v>
+        <v>926.6</v>
       </c>
       <c r="K115">
-        <v>1</v>
+        <v>1.0017</v>
       </c>
       <c r="L115">
-        <v>1.0001</v>
+        <v>1.0017</v>
       </c>
       <c r="M115">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="N115">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="O115">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>[-0.5470, -0.0704]</t>
+          <t>[-0.5529, -0.0508]</t>
         </is>
       </c>
     </row>
@@ -34214,35 +34214,35 @@
         </is>
       </c>
       <c r="G116">
-        <v>-1.666137154963477</v>
+        <v>-1.676201540987581</v>
       </c>
       <c r="H116">
-        <v>1.030182074355619</v>
+        <v>1.035283833008518</v>
       </c>
       <c r="I116">
-        <v>0.100866393262972</v>
+        <v>0.06791265277941498</v>
       </c>
       <c r="J116">
-        <v>104.3</v>
+        <v>232.4</v>
       </c>
       <c r="K116">
-        <v>1.0817</v>
+        <v>1.0198</v>
       </c>
       <c r="L116">
-        <v>1.0819</v>
+        <v>1.0199</v>
       </c>
       <c r="M116">
-        <v>-1.628339858179879</v>
+        <v>-1.675147167474839</v>
       </c>
       <c r="N116">
-        <v>-3.870161755723977</v>
+        <v>-3.805123165114205</v>
       </c>
       <c r="O116">
-        <v>0.1267385224481098</v>
+        <v>0.1771553118029174</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>[-3.8702, 0.1267]</t>
+          <t>[-3.8051, 0.1772]</t>
         </is>
       </c>
     </row>
@@ -34276,35 +34276,35 @@
         </is>
       </c>
       <c r="G117">
-        <v>0.06196936670816747</v>
+        <v>0.06535679301344875</v>
       </c>
       <c r="H117">
-        <v>0.0772600688734436</v>
+        <v>0.07677840040677844</v>
       </c>
       <c r="I117">
-        <v>0.002160805820487455</v>
+        <v>0.001474194024410116</v>
       </c>
       <c r="J117">
-        <v>1278.4</v>
+        <v>2712.5</v>
       </c>
       <c r="K117">
-        <v>1.0072</v>
+        <v>1.0006</v>
       </c>
       <c r="L117">
-        <v>1.0074</v>
+        <v>1.0007</v>
       </c>
       <c r="M117">
-        <v>0.06586546619170625</v>
+        <v>0.0686554630567057</v>
       </c>
       <c r="N117">
-        <v>-0.09540206644877555</v>
+        <v>-0.09582465412121587</v>
       </c>
       <c r="O117">
-        <v>0.2074720015902419</v>
+        <v>0.2083591378841529</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>[-0.0954, 0.2075]</t>
+          <t>[-0.0958, 0.2084]</t>
         </is>
       </c>
     </row>
@@ -34338,16 +34338,16 @@
         </is>
       </c>
       <c r="G118">
-        <v>-0.1046798152858951</v>
+        <v>-0.107017835387122</v>
       </c>
       <c r="H118">
-        <v>0.1301398294968226</v>
+        <v>0.1269459264510429</v>
       </c>
       <c r="I118">
-        <v>0.004153229807695243</v>
+        <v>0.002331311468511136</v>
       </c>
       <c r="J118">
-        <v>981.9</v>
+        <v>2965.1</v>
       </c>
       <c r="K118">
         <v>1</v>
@@ -34356,17 +34356,17 @@
         <v>1.0001</v>
       </c>
       <c r="M118">
-        <v>-0.1004581502557295</v>
+        <v>-0.1023315305345405</v>
       </c>
       <c r="N118">
-        <v>-0.3753464505385751</v>
+        <v>-0.3681489359962021</v>
       </c>
       <c r="O118">
-        <v>0.135475681257319</v>
+        <v>0.1248289554633815</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>[-0.3753, 0.1355]</t>
+          <t>[-0.3681, 0.1248]</t>
         </is>
       </c>
     </row>
@@ -34400,35 +34400,35 @@
         </is>
       </c>
       <c r="G119">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="H119">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="I119">
-        <v>0.02436067252164474</v>
+        <v>0.01616118574776551</v>
       </c>
       <c r="J119">
-        <v>104.3</v>
+        <v>243</v>
       </c>
       <c r="K119">
-        <v>1.0628</v>
+        <v>1.0136</v>
       </c>
       <c r="L119">
-        <v>1.063</v>
+        <v>1.0137</v>
       </c>
       <c r="M119">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="N119">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="O119">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>[-0.0167, 0.9905]</t>
+          <t>[0.0128, 1.0033]</t>
         </is>
       </c>
     </row>
@@ -34462,31 +34462,31 @@
         </is>
       </c>
       <c r="G120">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="H120">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="I120">
-        <v>7.424757282131184E-05</v>
+        <v>4.810704063421389E-05</v>
       </c>
       <c r="J120">
-        <v>1024.3</v>
+        <v>2479</v>
       </c>
       <c r="K120">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L120">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M120">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="N120">
-        <v>0.6577796351508191</v>
+        <v>0.6577717760918227</v>
       </c>
       <c r="O120">
-        <v>0.666602501839997</v>
+        <v>0.6665945953183382</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
@@ -34524,31 +34524,31 @@
         </is>
       </c>
       <c r="G121">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="H121">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="I121">
-        <v>7.424757282131176E-05</v>
+        <v>4.810704063421387E-05</v>
       </c>
       <c r="J121">
-        <v>1024.3</v>
+        <v>2479</v>
       </c>
       <c r="K121">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L121">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M121">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="N121">
-        <v>0.333397498160003</v>
+        <v>0.3334054046816618</v>
       </c>
       <c r="O121">
-        <v>0.342220364849181</v>
+        <v>0.3422282239081773</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
@@ -34586,35 +34586,35 @@
         </is>
       </c>
       <c r="G122">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="H122">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="I122">
-        <v>0.000338960358430166</v>
+        <v>0.0002197621614077366</v>
       </c>
       <c r="J122">
-        <v>1023.5</v>
+        <v>2473.4</v>
       </c>
       <c r="K122">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L122">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M122">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="N122">
-        <v>1.000288769513282</v>
+        <v>1.000324356132659</v>
       </c>
       <c r="O122">
-        <v>1.040531954963664</v>
+        <v>1.040568283247922</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>[1.0003, 1.0405]</t>
+          <t>[1.0003, 1.0406]</t>
         </is>
       </c>
     </row>
@@ -34648,16 +34648,16 @@
         </is>
       </c>
       <c r="G123">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="H123">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="I123">
-        <v>0.0003294579253450585</v>
+        <v>0.0002222946018841949</v>
       </c>
       <c r="J123">
-        <v>947</v>
+        <v>2327.8</v>
       </c>
       <c r="K123">
         <v>1</v>
@@ -34666,17 +34666,17 @@
         <v>1.0001</v>
       </c>
       <c r="M123">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="N123">
-        <v>0.0002449518806358951</v>
+        <v>0.0002856212000216427</v>
       </c>
       <c r="O123">
-        <v>0.03625229849217988</v>
+        <v>0.04007699114601319</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>[0.0002, 0.0363]</t>
+          <t>[0.0003, 0.0401]</t>
         </is>
       </c>
     </row>
@@ -34710,35 +34710,35 @@
         </is>
       </c>
       <c r="G124">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="H124">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="I124">
-        <v>1.996910908670789E-05</v>
+        <v>1.30210617703425E-05</v>
       </c>
       <c r="J124">
-        <v>1344.2</v>
+        <v>3318</v>
       </c>
       <c r="K124">
-        <v>1.0016</v>
+        <v>1.0007</v>
       </c>
       <c r="L124">
-        <v>1.0018</v>
+        <v>1.0008</v>
       </c>
       <c r="M124">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="N124">
-        <v>0.1242406376004758</v>
+        <v>0.1242264614416188</v>
       </c>
       <c r="O124">
-        <v>0.1270980490776865</v>
+        <v>0.1271816029686873</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>[0.1242, 0.1271]</t>
+          <t>[0.1242, 0.1272]</t>
         </is>
       </c>
     </row>
@@ -34772,31 +34772,31 @@
         </is>
       </c>
       <c r="G125">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="H125">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="I125">
-        <v>1.683505527229803E-05</v>
+        <v>1.020921344739324E-05</v>
       </c>
       <c r="J125">
-        <v>1041.4</v>
+        <v>2851.2</v>
       </c>
       <c r="K125">
-        <v>1.0008</v>
+        <v>1.0003</v>
       </c>
       <c r="L125">
-        <v>1.0009</v>
+        <v>1.0003</v>
       </c>
       <c r="M125">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="N125">
-        <v>0.06283446095178546</v>
+        <v>0.06283477689587211</v>
       </c>
       <c r="O125">
-        <v>0.06498835543089833</v>
+        <v>0.06500131971690672</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
@@ -34834,35 +34834,35 @@
         </is>
       </c>
       <c r="G126">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="H126">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="I126">
-        <v>7.287717726856617E-05</v>
+        <v>4.844680439743285E-05</v>
       </c>
       <c r="J126">
-        <v>1607</v>
+        <v>3850.4</v>
       </c>
       <c r="K126">
-        <v>1.0027</v>
+        <v>1.0002</v>
       </c>
       <c r="L126">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M126">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="N126">
-        <v>0.08530357549931405</v>
+        <v>0.08530411553282874</v>
       </c>
       <c r="O126">
-        <v>0.09676944586807242</v>
+        <v>0.09708120921233582</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>[0.0853, 0.0968]</t>
+          <t>[0.0853, 0.0971]</t>
         </is>
       </c>
     </row>
@@ -34896,31 +34896,31 @@
         </is>
       </c>
       <c r="G127">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="H127">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="I127">
-        <v>3.986943120105059E-05</v>
+        <v>2.631252420617495E-05</v>
       </c>
       <c r="J127">
-        <v>1488.3</v>
+        <v>3549.4</v>
       </c>
       <c r="K127">
-        <v>1.0026</v>
+        <v>1</v>
       </c>
       <c r="L127">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="M127">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="N127">
-        <v>0.04340335790008991</v>
+        <v>0.04337718702816454</v>
       </c>
       <c r="O127">
-        <v>0.04949428357228296</v>
+        <v>0.04953662420187081</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
@@ -34958,35 +34958,35 @@
         </is>
       </c>
       <c r="G128">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="H128">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="I128">
-        <v>0.0001029288770320282</v>
+        <v>6.927062815829008E-05</v>
       </c>
       <c r="J128">
-        <v>1613</v>
+        <v>3780.6</v>
       </c>
       <c r="K128">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="L128">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M128">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="N128">
-        <v>0.03999117999120268</v>
+        <v>0.03994847125857982</v>
       </c>
       <c r="O128">
-        <v>0.05616933018720535</v>
+        <v>0.05673759616221472</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>[0.0400, 0.0562]</t>
+          <t>[0.0399, 0.0567]</t>
         </is>
       </c>
     </row>
@@ -35020,35 +35020,35 @@
         </is>
       </c>
       <c r="G129">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="H129">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="I129">
-        <v>5.51738195653668E-05</v>
+        <v>3.693842765066764E-05</v>
       </c>
       <c r="J129">
-        <v>1543.5</v>
+        <v>3616</v>
       </c>
       <c r="K129">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L129">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M129">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="N129">
-        <v>0.02064486387576463</v>
+        <v>0.02057363057052737</v>
       </c>
       <c r="O129">
-        <v>0.02922876830495247</v>
+        <v>0.02929047714320697</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>[0.0206, 0.0292]</t>
+          <t>[0.0206, 0.0293]</t>
         </is>
       </c>
     </row>
@@ -35082,35 +35082,35 @@
         </is>
       </c>
       <c r="G130">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="H130">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="I130">
-        <v>7.654870579497798E-05</v>
+        <v>5.163247376084753E-05</v>
       </c>
       <c r="J130">
-        <v>1618.5</v>
+        <v>3800.1</v>
       </c>
       <c r="K130">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L130">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M130">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="N130">
-        <v>0.01283181136513961</v>
+        <v>0.01279121060028293</v>
       </c>
       <c r="O130">
-        <v>0.02486300206783066</v>
+        <v>0.02534096888804091</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>[0.0128, 0.0249]</t>
+          <t>[0.0128, 0.0253]</t>
         </is>
       </c>
     </row>
@@ -35144,35 +35144,35 @@
         </is>
       </c>
       <c r="G131">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="H131">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="I131">
-        <v>4.173482703340465E-05</v>
+        <v>2.809001079626773E-05</v>
       </c>
       <c r="J131">
-        <v>1549.7</v>
+        <v>3629</v>
       </c>
       <c r="K131">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L131">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M131">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="N131">
-        <v>0.006754465912628241</v>
+        <v>0.006711515300852532</v>
       </c>
       <c r="O131">
-        <v>0.01324374278248805</v>
+        <v>0.01334017469519632</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>[0.0068, 0.0132]</t>
+          <t>[0.0067, 0.0133]</t>
         </is>
       </c>
     </row>
@@ -35206,35 +35206,35 @@
         </is>
       </c>
       <c r="G132">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="H132">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="I132">
-        <v>3.545284751407308E-05</v>
+        <v>2.416065724367434E-05</v>
       </c>
       <c r="J132">
-        <v>1631.4</v>
+        <v>3795.6</v>
       </c>
       <c r="K132">
-        <v>1.0025</v>
+        <v>1.0001</v>
       </c>
       <c r="L132">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="M132">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="N132">
-        <v>0.002821790209533828</v>
+        <v>0.002799332792224822</v>
       </c>
       <c r="O132">
-        <v>0.008395180840575273</v>
+        <v>0.008648722296811141</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>[0.0028, 0.0084]</t>
+          <t>[0.0028, 0.0086]</t>
         </is>
       </c>
     </row>
@@ -35268,35 +35268,35 @@
         </is>
       </c>
       <c r="G133">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="H133">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="I133">
-        <v>1.984959082910289E-05</v>
+        <v>1.348852967546526E-05</v>
       </c>
       <c r="J133">
-        <v>1560.3</v>
+        <v>3641.1</v>
       </c>
       <c r="K133">
-        <v>1.0025</v>
+        <v>1.0001</v>
       </c>
       <c r="L133">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="M133">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="N133">
-        <v>0.001519424188693608</v>
+        <v>0.00150537464286404</v>
       </c>
       <c r="O133">
-        <v>0.004612211856696236</v>
+        <v>0.004672985536810267</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>[0.0015, 0.0046]</t>
+          <t>[0.0015, 0.0047]</t>
         </is>
       </c>
     </row>
@@ -35330,35 +35330,35 @@
         </is>
       </c>
       <c r="G134">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="H134">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="I134">
-        <v>0.0378516379781366</v>
+        <v>0.02550205715002106</v>
       </c>
       <c r="J134">
-        <v>1614.6</v>
+        <v>3787.6</v>
       </c>
       <c r="K134">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L134">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M134">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="N134">
-        <v>31.99254556149809</v>
+        <v>31.94745644144655</v>
       </c>
       <c r="O134">
-        <v>37.93542068119201</v>
+        <v>38.14741835772089</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>[31.9925, 37.9354]</t>
+          <t>[31.9475, 38.1474]</t>
         </is>
       </c>
     </row>
@@ -35392,35 +35392,35 @@
         </is>
       </c>
       <c r="G135">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="H135">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="I135">
-        <v>0.04030004615481509</v>
+        <v>0.02712816536419896</v>
       </c>
       <c r="J135">
-        <v>1551.4</v>
+        <v>3630.6</v>
       </c>
       <c r="K135">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L135">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M135">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="N135">
-        <v>32.24875528724777</v>
+        <v>32.21258652369725</v>
       </c>
       <c r="O135">
-        <v>38.52489088509614</v>
+        <v>38.63563343246012</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>[32.2488, 38.5249]</t>
+          <t>[32.2126, 38.6356]</t>
         </is>
       </c>
     </row>
@@ -35454,35 +35454,35 @@
         </is>
       </c>
       <c r="G136">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="H136">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="I136">
-        <v>0.001085847783755566</v>
+        <v>0.0007306544822292565</v>
       </c>
       <c r="J136">
-        <v>1612.6</v>
+        <v>3778.7</v>
       </c>
       <c r="K136">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="L136">
-        <v>1.0029</v>
+        <v>1.0002</v>
       </c>
       <c r="M136">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="N136">
-        <v>3.465502924459196</v>
+        <v>3.464092567052742</v>
       </c>
       <c r="O136">
-        <v>3.635885258255161</v>
+        <v>3.641458084607688</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>[3.4655, 3.6359]</t>
+          <t>[3.4641, 3.6415]</t>
         </is>
       </c>
     </row>
@@ -35516,31 +35516,31 @@
         </is>
       </c>
       <c r="G137">
-        <v>1.589311306603231</v>
+        <v>1.589395984848507</v>
       </c>
       <c r="H137">
-        <v>0.007205628292603781</v>
+        <v>0.007262318948204624</v>
       </c>
       <c r="I137">
-        <v>0.0002252675616788616</v>
+        <v>0.0001460825366373568</v>
       </c>
       <c r="J137">
-        <v>1023.2</v>
+        <v>2471.5</v>
       </c>
       <c r="K137">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L137">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M137">
-        <v>1.587119633634973</v>
+        <v>1.587220493981195</v>
       </c>
       <c r="N137">
-        <v>1.582167677340778</v>
+        <v>1.582191212529661</v>
       </c>
       <c r="O137">
-        <v>1.608904274809916</v>
+        <v>1.608928520286697</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
@@ -35578,35 +35578,35 @@
         </is>
       </c>
       <c r="G138">
-        <v>14087.40902959247</v>
+        <v>14123.64149129999</v>
       </c>
       <c r="H138">
-        <v>1445.727510630541</v>
+        <v>1498.001853014637</v>
       </c>
       <c r="I138">
-        <v>52.71048431542673</v>
+        <v>36.50273536976891</v>
       </c>
       <c r="J138">
-        <v>752.3</v>
+        <v>1684.1</v>
       </c>
       <c r="K138">
-        <v>1.0016</v>
+        <v>1.0007</v>
       </c>
       <c r="L138">
-        <v>1.0018</v>
+        <v>1.0008</v>
       </c>
       <c r="M138">
-        <v>13992.38790436515</v>
+        <v>14004.29100480898</v>
       </c>
       <c r="N138">
-        <v>11588.8616471647</v>
+        <v>11516.91198988923</v>
       </c>
       <c r="O138">
-        <v>17266.52511340762</v>
+        <v>17387.29688123515</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>[11588.8616, 17266.5251]</t>
+          <t>[11516.9120, 17387.2969]</t>
         </is>
       </c>
     </row>
@@ -35640,35 +35640,35 @@
         </is>
       </c>
       <c r="G139">
-        <v>0.3113032558764295</v>
+        <v>0.3232031014683357</v>
       </c>
       <c r="H139">
-        <v>0.1362093634617424</v>
+        <v>0.1420946102486272</v>
       </c>
       <c r="I139">
-        <v>0.007187725811170085</v>
+        <v>0.005248126246874685</v>
       </c>
       <c r="J139">
-        <v>359.1</v>
+        <v>733.1</v>
       </c>
       <c r="K139">
-        <v>1.021</v>
+        <v>1.0073</v>
       </c>
       <c r="L139">
-        <v>1.0212</v>
+        <v>1.0074</v>
       </c>
       <c r="M139">
-        <v>0.316257303341141</v>
+        <v>0.329737376709393</v>
       </c>
       <c r="N139">
-        <v>0.02694270680745655</v>
+        <v>0.02380958686559168</v>
       </c>
       <c r="O139">
-        <v>0.5693657637896794</v>
+        <v>0.5866353602915522</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>[0.0269, 0.5694]</t>
+          <t>[0.0238, 0.5866]</t>
         </is>
       </c>
     </row>
@@ -35702,35 +35702,35 @@
         </is>
       </c>
       <c r="G140">
-        <v>-0.1161112990728373</v>
+        <v>-0.1287407946727498</v>
       </c>
       <c r="H140">
-        <v>0.1148021978489128</v>
+        <v>0.1205661088449834</v>
       </c>
       <c r="I140">
-        <v>0.004777383282242065</v>
+        <v>0.003673175758948686</v>
       </c>
       <c r="J140">
-        <v>577.5</v>
+        <v>1077.4</v>
       </c>
       <c r="K140">
-        <v>1.0004</v>
+        <v>1.0005</v>
       </c>
       <c r="L140">
         <v>1.0006</v>
       </c>
       <c r="M140">
-        <v>-0.1133521931553859</v>
+        <v>-0.1273749279336696</v>
       </c>
       <c r="N140">
-        <v>-0.3386719515336633</v>
+        <v>-0.3651564914560492</v>
       </c>
       <c r="O140">
-        <v>0.1091078866312331</v>
+        <v>0.1069579387757273</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>[-0.3387, 0.1091]</t>
+          <t>[-0.3652, 0.1070]</t>
         </is>
       </c>
     </row>
@@ -35764,35 +35764,35 @@
         </is>
       </c>
       <c r="G141">
-        <v>-0.5116146559729645</v>
+        <v>-0.5369591626463901</v>
       </c>
       <c r="H141">
-        <v>0.1871635112221394</v>
+        <v>0.2036126439218424</v>
       </c>
       <c r="I141">
-        <v>0.01356939193655912</v>
+        <v>0.009715251156275482</v>
       </c>
       <c r="J141">
-        <v>190.2</v>
+        <v>439.2</v>
       </c>
       <c r="K141">
-        <v>1.0055</v>
+        <v>1.005</v>
       </c>
       <c r="L141">
-        <v>1.0057</v>
+        <v>1.005</v>
       </c>
       <c r="M141">
-        <v>-0.5231870318312245</v>
+        <v>-0.5428493951436821</v>
       </c>
       <c r="N141">
-        <v>-0.8514261295155847</v>
+        <v>-0.9272919620447222</v>
       </c>
       <c r="O141">
-        <v>-0.1024529610643907</v>
+        <v>-0.1120617046669647</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>[-0.8514, -0.1025]</t>
+          <t>[-0.9273, -0.1121]</t>
         </is>
       </c>
     </row>
@@ -35826,35 +35826,35 @@
         </is>
       </c>
       <c r="G142">
-        <v>-0.2997581758479709</v>
+        <v>-0.2914665335266804</v>
       </c>
       <c r="H142">
-        <v>0.1205935446563193</v>
+        <v>0.1268638371184199</v>
       </c>
       <c r="I142">
-        <v>0.005794357245884296</v>
+        <v>0.004167663529072831</v>
       </c>
       <c r="J142">
-        <v>433.1</v>
+        <v>926.6</v>
       </c>
       <c r="K142">
-        <v>1</v>
+        <v>1.0017</v>
       </c>
       <c r="L142">
-        <v>1.0001</v>
+        <v>1.0017</v>
       </c>
       <c r="M142">
-        <v>-0.3003177394172399</v>
+        <v>-0.2881630288386164</v>
       </c>
       <c r="N142">
-        <v>-0.5470176895445191</v>
+        <v>-0.5529306099134519</v>
       </c>
       <c r="O142">
-        <v>-0.07035117526766081</v>
+        <v>-0.05075267660401554</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>[-0.5470, -0.0704]</t>
+          <t>[-0.5529, -0.0508]</t>
         </is>
       </c>
     </row>
@@ -35888,35 +35888,35 @@
         </is>
       </c>
       <c r="G143">
-        <v>-1.666137154963477</v>
+        <v>-1.676201540987581</v>
       </c>
       <c r="H143">
-        <v>1.030182074355619</v>
+        <v>1.035283833008518</v>
       </c>
       <c r="I143">
-        <v>0.100866393262972</v>
+        <v>0.06791265277941498</v>
       </c>
       <c r="J143">
-        <v>104.3</v>
+        <v>232.4</v>
       </c>
       <c r="K143">
-        <v>1.0817</v>
+        <v>1.0198</v>
       </c>
       <c r="L143">
-        <v>1.0819</v>
+        <v>1.0199</v>
       </c>
       <c r="M143">
-        <v>-1.628339858179879</v>
+        <v>-1.675147167474839</v>
       </c>
       <c r="N143">
-        <v>-3.870161755723977</v>
+        <v>-3.805123165114205</v>
       </c>
       <c r="O143">
-        <v>0.1267385224481098</v>
+        <v>0.1771553118029174</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>[-3.8702, 0.1267]</t>
+          <t>[-3.8051, 0.1772]</t>
         </is>
       </c>
     </row>
@@ -35950,35 +35950,35 @@
         </is>
       </c>
       <c r="G144">
-        <v>0.06196936670816747</v>
+        <v>0.06535679301344875</v>
       </c>
       <c r="H144">
-        <v>0.0772600688734436</v>
+        <v>0.07677840040677844</v>
       </c>
       <c r="I144">
-        <v>0.002160805820487455</v>
+        <v>0.001474194024410116</v>
       </c>
       <c r="J144">
-        <v>1278.4</v>
+        <v>2712.5</v>
       </c>
       <c r="K144">
-        <v>1.0072</v>
+        <v>1.0006</v>
       </c>
       <c r="L144">
-        <v>1.0074</v>
+        <v>1.0007</v>
       </c>
       <c r="M144">
-        <v>0.06586546619170625</v>
+        <v>0.0686554630567057</v>
       </c>
       <c r="N144">
-        <v>-0.09540206644877555</v>
+        <v>-0.09582465412121587</v>
       </c>
       <c r="O144">
-        <v>0.2074720015902419</v>
+        <v>0.2083591378841529</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>[-0.0954, 0.2075]</t>
+          <t>[-0.0958, 0.2084]</t>
         </is>
       </c>
     </row>
@@ -36012,16 +36012,16 @@
         </is>
       </c>
       <c r="G145">
-        <v>-0.1046798152858951</v>
+        <v>-0.107017835387122</v>
       </c>
       <c r="H145">
-        <v>0.1301398294968226</v>
+        <v>0.1269459264510429</v>
       </c>
       <c r="I145">
-        <v>0.004153229807695243</v>
+        <v>0.002331311468511136</v>
       </c>
       <c r="J145">
-        <v>981.9</v>
+        <v>2965.1</v>
       </c>
       <c r="K145">
         <v>1</v>
@@ -36030,17 +36030,17 @@
         <v>1.0001</v>
       </c>
       <c r="M145">
-        <v>-0.1004581502557295</v>
+        <v>-0.1023315305345405</v>
       </c>
       <c r="N145">
-        <v>-0.3753464505385751</v>
+        <v>-0.3681489359962021</v>
       </c>
       <c r="O145">
-        <v>0.135475681257319</v>
+        <v>0.1248289554633815</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>[-0.3753, 0.1355]</t>
+          <t>[-0.3681, 0.1248]</t>
         </is>
       </c>
     </row>
@@ -36074,35 +36074,35 @@
         </is>
       </c>
       <c r="G146">
-        <v>0.5417060408592684</v>
+        <v>0.5336913927167031</v>
       </c>
       <c r="H146">
-        <v>0.2487964918880957</v>
+        <v>0.2519487102677469</v>
       </c>
       <c r="I146">
-        <v>0.02436067252164474</v>
+        <v>0.01616118574776551</v>
       </c>
       <c r="J146">
-        <v>104.3</v>
+        <v>243</v>
       </c>
       <c r="K146">
-        <v>1.0628</v>
+        <v>1.0136</v>
       </c>
       <c r="L146">
-        <v>1.063</v>
+        <v>1.0137</v>
       </c>
       <c r="M146">
-        <v>0.5604503041457983</v>
+        <v>0.5420514501089884</v>
       </c>
       <c r="N146">
-        <v>-0.01666641103674497</v>
+        <v>0.01280902634430924</v>
       </c>
       <c r="O146">
-        <v>0.9904871377410074</v>
+        <v>1.003268729594857</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>[-0.0167, 0.9905]</t>
+          <t>[0.0128, 1.0033]</t>
         </is>
       </c>
     </row>
@@ -36136,31 +36136,31 @@
         </is>
       </c>
       <c r="G147">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="H147">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="I147">
-        <v>7.424757282131184E-05</v>
+        <v>4.810704063421389E-05</v>
       </c>
       <c r="J147">
-        <v>1024.3</v>
+        <v>2479</v>
       </c>
       <c r="K147">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L147">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M147">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="N147">
-        <v>0.6577796351508191</v>
+        <v>0.6577717760918227</v>
       </c>
       <c r="O147">
-        <v>0.666602501839997</v>
+        <v>0.6665945953183382</v>
       </c>
       <c r="P147" t="inlineStr">
         <is>
@@ -36198,31 +36198,31 @@
         </is>
       </c>
       <c r="G148">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="H148">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="I148">
-        <v>7.424757282131176E-05</v>
+        <v>4.810704063421387E-05</v>
       </c>
       <c r="J148">
-        <v>1024.3</v>
+        <v>2479</v>
       </c>
       <c r="K148">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L148">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M148">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="N148">
-        <v>0.333397498160003</v>
+        <v>0.3334054046816618</v>
       </c>
       <c r="O148">
-        <v>0.342220364849181</v>
+        <v>0.3422282239081773</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
@@ -36260,35 +36260,35 @@
         </is>
       </c>
       <c r="G149">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="H149">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="I149">
-        <v>0.000338960358430166</v>
+        <v>0.0002197621614077366</v>
       </c>
       <c r="J149">
-        <v>1023.5</v>
+        <v>2473.4</v>
       </c>
       <c r="K149">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L149">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M149">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="N149">
-        <v>1.000288769513282</v>
+        <v>1.000324356132659</v>
       </c>
       <c r="O149">
-        <v>1.040531954963664</v>
+        <v>1.040568283247922</v>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>[1.0003, 1.0405]</t>
+          <t>[1.0003, 1.0406]</t>
         </is>
       </c>
     </row>
@@ -36322,16 +36322,16 @@
         </is>
       </c>
       <c r="G150">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="H150">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="I150">
-        <v>0.0003294579253450585</v>
+        <v>0.0002222946018841949</v>
       </c>
       <c r="J150">
-        <v>947</v>
+        <v>2327.8</v>
       </c>
       <c r="K150">
         <v>1</v>
@@ -36340,17 +36340,17 @@
         <v>1.0001</v>
       </c>
       <c r="M150">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="N150">
-        <v>0.0002449518806358951</v>
+        <v>0.0002856212000216427</v>
       </c>
       <c r="O150">
-        <v>0.03625229849217988</v>
+        <v>0.04007699114601319</v>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>[0.0002, 0.0363]</t>
+          <t>[0.0003, 0.0401]</t>
         </is>
       </c>
     </row>
@@ -36384,35 +36384,35 @@
         </is>
       </c>
       <c r="G151">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="H151">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="I151">
-        <v>1.996910908670789E-05</v>
+        <v>1.30210617703425E-05</v>
       </c>
       <c r="J151">
-        <v>1344.2</v>
+        <v>3318</v>
       </c>
       <c r="K151">
-        <v>1.0016</v>
+        <v>1.0007</v>
       </c>
       <c r="L151">
-        <v>1.0018</v>
+        <v>1.0008</v>
       </c>
       <c r="M151">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="N151">
-        <v>0.1242406376004758</v>
+        <v>0.1242264614416188</v>
       </c>
       <c r="O151">
-        <v>0.1270980490776865</v>
+        <v>0.1271816029686873</v>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>[0.1242, 0.1271]</t>
+          <t>[0.1242, 0.1272]</t>
         </is>
       </c>
     </row>
@@ -36446,31 +36446,31 @@
         </is>
       </c>
       <c r="G152">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="H152">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="I152">
-        <v>1.683505527229803E-05</v>
+        <v>1.020921344739324E-05</v>
       </c>
       <c r="J152">
-        <v>1041.4</v>
+        <v>2851.2</v>
       </c>
       <c r="K152">
-        <v>1.0008</v>
+        <v>1.0003</v>
       </c>
       <c r="L152">
-        <v>1.0009</v>
+        <v>1.0003</v>
       </c>
       <c r="M152">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="N152">
-        <v>0.06283446095178546</v>
+        <v>0.06283477689587211</v>
       </c>
       <c r="O152">
-        <v>0.06498835543089833</v>
+        <v>0.06500131971690672</v>
       </c>
       <c r="P152" t="inlineStr">
         <is>
@@ -36508,35 +36508,35 @@
         </is>
       </c>
       <c r="G153">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="H153">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="I153">
-        <v>7.287717726856617E-05</v>
+        <v>4.844680439743285E-05</v>
       </c>
       <c r="J153">
-        <v>1607</v>
+        <v>3850.4</v>
       </c>
       <c r="K153">
-        <v>1.0027</v>
+        <v>1.0002</v>
       </c>
       <c r="L153">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M153">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="N153">
-        <v>0.08530357549931405</v>
+        <v>0.08530411553282874</v>
       </c>
       <c r="O153">
-        <v>0.09676944586807242</v>
+        <v>0.09708120921233582</v>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>[0.0853, 0.0968]</t>
+          <t>[0.0853, 0.0971]</t>
         </is>
       </c>
     </row>
@@ -36570,31 +36570,31 @@
         </is>
       </c>
       <c r="G154">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="H154">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="I154">
-        <v>3.986943120105059E-05</v>
+        <v>2.631252420617495E-05</v>
       </c>
       <c r="J154">
-        <v>1488.3</v>
+        <v>3549.4</v>
       </c>
       <c r="K154">
-        <v>1.0026</v>
+        <v>1</v>
       </c>
       <c r="L154">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="M154">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="N154">
-        <v>0.04340335790008991</v>
+        <v>0.04337718702816454</v>
       </c>
       <c r="O154">
-        <v>0.04949428357228296</v>
+        <v>0.04953662420187081</v>
       </c>
       <c r="P154" t="inlineStr">
         <is>
@@ -36632,35 +36632,35 @@
         </is>
       </c>
       <c r="G155">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="H155">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="I155">
-        <v>0.0001029288770320282</v>
+        <v>6.927062815829008E-05</v>
       </c>
       <c r="J155">
-        <v>1613</v>
+        <v>3780.6</v>
       </c>
       <c r="K155">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="L155">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M155">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="N155">
-        <v>0.03999117999120268</v>
+        <v>0.03994847125857982</v>
       </c>
       <c r="O155">
-        <v>0.05616933018720535</v>
+        <v>0.05673759616221472</v>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>[0.0400, 0.0562]</t>
+          <t>[0.0399, 0.0567]</t>
         </is>
       </c>
     </row>
@@ -36694,35 +36694,35 @@
         </is>
       </c>
       <c r="G156">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="H156">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="I156">
-        <v>5.51738195653668E-05</v>
+        <v>3.693842765066764E-05</v>
       </c>
       <c r="J156">
-        <v>1543.5</v>
+        <v>3616</v>
       </c>
       <c r="K156">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L156">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M156">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="N156">
-        <v>0.02064486387576463</v>
+        <v>0.02057363057052737</v>
       </c>
       <c r="O156">
-        <v>0.02922876830495247</v>
+        <v>0.02929047714320697</v>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>[0.0206, 0.0292]</t>
+          <t>[0.0206, 0.0293]</t>
         </is>
       </c>
     </row>
@@ -36756,35 +36756,35 @@
         </is>
       </c>
       <c r="G157">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="H157">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="I157">
-        <v>7.654870579497798E-05</v>
+        <v>5.163247376084753E-05</v>
       </c>
       <c r="J157">
-        <v>1618.5</v>
+        <v>3800.1</v>
       </c>
       <c r="K157">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L157">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M157">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="N157">
-        <v>0.01283181136513961</v>
+        <v>0.01279121060028293</v>
       </c>
       <c r="O157">
-        <v>0.02486300206783066</v>
+        <v>0.02534096888804091</v>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>[0.0128, 0.0249]</t>
+          <t>[0.0128, 0.0253]</t>
         </is>
       </c>
     </row>
@@ -36818,35 +36818,35 @@
         </is>
       </c>
       <c r="G158">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="H158">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="I158">
-        <v>4.173482703340465E-05</v>
+        <v>2.809001079626773E-05</v>
       </c>
       <c r="J158">
-        <v>1549.7</v>
+        <v>3629</v>
       </c>
       <c r="K158">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L158">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M158">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="N158">
-        <v>0.006754465912628241</v>
+        <v>0.006711515300852532</v>
       </c>
       <c r="O158">
-        <v>0.01324374278248805</v>
+        <v>0.01334017469519632</v>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>[0.0068, 0.0132]</t>
+          <t>[0.0067, 0.0133]</t>
         </is>
       </c>
     </row>
@@ -36880,35 +36880,35 @@
         </is>
       </c>
       <c r="G159">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="H159">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="I159">
-        <v>3.545284751407308E-05</v>
+        <v>2.416065724367434E-05</v>
       </c>
       <c r="J159">
-        <v>1631.4</v>
+        <v>3795.6</v>
       </c>
       <c r="K159">
-        <v>1.0025</v>
+        <v>1.0001</v>
       </c>
       <c r="L159">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="M159">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="N159">
-        <v>0.002821790209533828</v>
+        <v>0.002799332792224822</v>
       </c>
       <c r="O159">
-        <v>0.008395180840575273</v>
+        <v>0.008648722296811141</v>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>[0.0028, 0.0084]</t>
+          <t>[0.0028, 0.0086]</t>
         </is>
       </c>
     </row>
@@ -36942,35 +36942,35 @@
         </is>
       </c>
       <c r="G160">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="H160">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="I160">
-        <v>1.984959082910289E-05</v>
+        <v>1.348852967546526E-05</v>
       </c>
       <c r="J160">
-        <v>1560.3</v>
+        <v>3641.1</v>
       </c>
       <c r="K160">
-        <v>1.0025</v>
+        <v>1.0001</v>
       </c>
       <c r="L160">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="M160">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="N160">
-        <v>0.001519424188693608</v>
+        <v>0.00150537464286404</v>
       </c>
       <c r="O160">
-        <v>0.004612211856696236</v>
+        <v>0.004672985536810267</v>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>[0.0015, 0.0046]</t>
+          <t>[0.0015, 0.0047]</t>
         </is>
       </c>
     </row>
@@ -37004,35 +37004,35 @@
         </is>
       </c>
       <c r="G161">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="H161">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="I161">
-        <v>0.0378516379781366</v>
+        <v>0.02550205715002106</v>
       </c>
       <c r="J161">
-        <v>1614.6</v>
+        <v>3787.6</v>
       </c>
       <c r="K161">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L161">
-        <v>1.0028</v>
+        <v>1.0001</v>
       </c>
       <c r="M161">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="N161">
-        <v>31.99254556149809</v>
+        <v>31.94745644144655</v>
       </c>
       <c r="O161">
-        <v>37.93542068119201</v>
+        <v>38.14741835772089</v>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>[31.9925, 37.9354]</t>
+          <t>[31.9475, 38.1474]</t>
         </is>
       </c>
     </row>
@@ -37066,35 +37066,35 @@
         </is>
       </c>
       <c r="G162">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="H162">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="I162">
-        <v>0.04030004615481509</v>
+        <v>0.02712816536419896</v>
       </c>
       <c r="J162">
-        <v>1551.4</v>
+        <v>3630.6</v>
       </c>
       <c r="K162">
-        <v>1.0026</v>
+        <v>1.0001</v>
       </c>
       <c r="L162">
-        <v>1.0028</v>
+        <v>1.0002</v>
       </c>
       <c r="M162">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="N162">
-        <v>32.24875528724777</v>
+        <v>32.21258652369725</v>
       </c>
       <c r="O162">
-        <v>38.52489088509614</v>
+        <v>38.63563343246012</v>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>[32.2488, 38.5249]</t>
+          <t>[32.2126, 38.6356]</t>
         </is>
       </c>
     </row>
@@ -37128,35 +37128,35 @@
         </is>
       </c>
       <c r="G163">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="H163">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="I163">
-        <v>0.001085847783755566</v>
+        <v>0.0007306544822292565</v>
       </c>
       <c r="J163">
-        <v>1612.6</v>
+        <v>3778.7</v>
       </c>
       <c r="K163">
-        <v>1.0027</v>
+        <v>1.0001</v>
       </c>
       <c r="L163">
-        <v>1.0029</v>
+        <v>1.0002</v>
       </c>
       <c r="M163">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="N163">
-        <v>3.465502924459196</v>
+        <v>3.464092567052742</v>
       </c>
       <c r="O163">
-        <v>3.635885258255161</v>
+        <v>3.641458084607688</v>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>[3.4655, 3.6359]</t>
+          <t>[3.4641, 3.6415]</t>
         </is>
       </c>
     </row>
@@ -37190,35 +37190,35 @@
         </is>
       </c>
       <c r="G164">
-        <v>1.589640334434895</v>
+        <v>1.589174854119623</v>
       </c>
       <c r="H164">
-        <v>0.00795121676506972</v>
+        <v>0.007148989996426714</v>
       </c>
       <c r="I164">
-        <v>0.0002805201755568651</v>
+        <v>0.0001456867702393411</v>
       </c>
       <c r="J164">
-        <v>803.4</v>
+        <v>2408</v>
       </c>
       <c r="K164">
-        <v>1.0005</v>
+        <v>1</v>
       </c>
       <c r="L164">
-        <v>1.0007</v>
+        <v>1.0001</v>
       </c>
       <c r="M164">
-        <v>1.587427023153701</v>
+        <v>1.587030738163915</v>
       </c>
       <c r="N164">
-        <v>1.582144908379842</v>
+        <v>1.582160112817667</v>
       </c>
       <c r="O164">
-        <v>1.611390013822537</v>
+        <v>1.608543112262572</v>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>[1.5821, 1.6114]</t>
+          <t>[1.5822, 1.6085]</t>
         </is>
       </c>
     </row>
@@ -37252,35 +37252,35 @@
         </is>
       </c>
       <c r="G165">
-        <v>14027.33621351519</v>
+        <v>14216.02533528759</v>
       </c>
       <c r="H165">
-        <v>1363.431242925964</v>
+        <v>1455.366791299486</v>
       </c>
       <c r="I165">
-        <v>68.13676959264878</v>
+        <v>52.36018113213589</v>
       </c>
       <c r="J165">
-        <v>400.4</v>
+        <v>772.6</v>
       </c>
       <c r="K165">
-        <v>1.0021</v>
+        <v>1.0136</v>
       </c>
       <c r="L165">
-        <v>1.0023</v>
+        <v>1.0137</v>
       </c>
       <c r="M165">
-        <v>13946.0791383601</v>
+        <v>14095.9234672661</v>
       </c>
       <c r="N165">
-        <v>11576.60961226968</v>
+        <v>11752.38279582354</v>
       </c>
       <c r="O165">
-        <v>16976.35717694564</v>
+        <v>17451.78245111521</v>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>[11576.6096, 16976.3572]</t>
+          <t>[11752.3828, 17451.7825]</t>
         </is>
       </c>
     </row>
@@ -37314,35 +37314,35 @@
         </is>
       </c>
       <c r="G166">
-        <v>-0.01826005027217653</v>
+        <v>-0.004944831113370689</v>
       </c>
       <c r="H166">
-        <v>1.511863238131528</v>
+        <v>1.503324674485275</v>
       </c>
       <c r="I166">
-        <v>0.028895922319019</v>
+        <v>0.01795323413073995</v>
       </c>
       <c r="J166">
-        <v>2737.5</v>
+        <v>7011.6</v>
       </c>
       <c r="K166">
-        <v>1</v>
+        <v>1.0002</v>
       </c>
       <c r="L166">
-        <v>1.0001</v>
+        <v>1.0003</v>
       </c>
       <c r="M166">
-        <v>-0.01200833206057261</v>
+        <v>0.004377560290349192</v>
       </c>
       <c r="N166">
-        <v>-3.005835895115747</v>
+        <v>-2.95980901421379</v>
       </c>
       <c r="O166">
-        <v>3.028902554939272</v>
+        <v>2.893596351326704</v>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>[-3.0058, 3.0289]</t>
+          <t>[-2.9598, 2.8936]</t>
         </is>
       </c>
     </row>
@@ -37376,35 +37376,35 @@
         </is>
       </c>
       <c r="G167">
-        <v>-0.0428691463641525</v>
+        <v>0.006081323749867635</v>
       </c>
       <c r="H167">
-        <v>1.485435370135724</v>
+        <v>1.508643208735099</v>
       </c>
       <c r="I167">
-        <v>0.02787809449414519</v>
+        <v>0.01797387789654757</v>
       </c>
       <c r="J167">
-        <v>2839.1</v>
+        <v>7045.1</v>
       </c>
       <c r="K167">
-        <v>1.0002</v>
+        <v>1</v>
       </c>
       <c r="L167">
-        <v>1.0004</v>
+        <v>1</v>
       </c>
       <c r="M167">
-        <v>-0.05823552455530573</v>
+        <v>0.01249325292684678</v>
       </c>
       <c r="N167">
-        <v>-2.942457407156066</v>
+        <v>-3.011495432093967</v>
       </c>
       <c r="O167">
-        <v>2.815865376647903</v>
+        <v>2.929819569434809</v>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>[-2.9425, 2.8159]</t>
+          <t>[-3.0115, 2.9298]</t>
         </is>
       </c>
     </row>
@@ -37438,35 +37438,35 @@
         </is>
       </c>
       <c r="G168">
-        <v>-0.04244408909561401</v>
+        <v>0.02949416802146175</v>
       </c>
       <c r="H168">
-        <v>1.549254894857014</v>
+        <v>1.478440767727238</v>
       </c>
       <c r="I168">
-        <v>0.02958687882339335</v>
+        <v>0.01759857772747362</v>
       </c>
       <c r="J168">
-        <v>2741.9</v>
+        <v>7057.5</v>
       </c>
       <c r="K168">
         <v>1</v>
       </c>
       <c r="L168">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="M168">
-        <v>-0.05391741794427474</v>
+        <v>0.04605303253774173</v>
       </c>
       <c r="N168">
-        <v>-3.024668719333336</v>
+        <v>-2.907944037383172</v>
       </c>
       <c r="O168">
-        <v>3.024145567926314</v>
+        <v>2.88333269800643</v>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>[-3.0247, 3.0241]</t>
+          <t>[-2.9079, 2.8833]</t>
         </is>
       </c>
     </row>
@@ -37500,35 +37500,35 @@
         </is>
       </c>
       <c r="G169">
-        <v>-0.4065596936517923</v>
+        <v>-0.3861219822456349</v>
       </c>
       <c r="H169">
-        <v>0.1367732975379721</v>
+        <v>0.1375031246846421</v>
       </c>
       <c r="I169">
-        <v>0.007840417401125482</v>
+        <v>0.005285119712118938</v>
       </c>
       <c r="J169">
-        <v>304.3</v>
+        <v>676.9</v>
       </c>
       <c r="K169">
-        <v>1.0521</v>
+        <v>1.0056</v>
       </c>
       <c r="L169">
-        <v>1.0523</v>
+        <v>1.0056</v>
       </c>
       <c r="M169">
-        <v>-0.4059009629105702</v>
+        <v>-0.3844796819927853</v>
       </c>
       <c r="N169">
-        <v>-0.6808653523379501</v>
+        <v>-0.660343584330276</v>
       </c>
       <c r="O169">
-        <v>-0.13768853671991</v>
+        <v>-0.1103279673395892</v>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>[-0.6809, -0.1377]</t>
+          <t>[-0.6603, -0.1103]</t>
         </is>
       </c>
     </row>
@@ -37562,35 +37562,35 @@
         </is>
       </c>
       <c r="G170">
-        <v>0.02911945967003693</v>
+        <v>0.001506180379860736</v>
       </c>
       <c r="H170">
-        <v>1.467685853770194</v>
+        <v>1.488009989262242</v>
       </c>
       <c r="I170">
-        <v>0.02680159465390105</v>
+        <v>0.01773859462325813</v>
       </c>
       <c r="J170">
-        <v>2998.8</v>
+        <v>7036.8</v>
       </c>
       <c r="K170">
-        <v>1.0003</v>
+        <v>1.0001</v>
       </c>
       <c r="L170">
-        <v>1.0004</v>
+        <v>1.0002</v>
       </c>
       <c r="M170">
-        <v>-0.004218229860793565</v>
+        <v>-0.009339186512010933</v>
       </c>
       <c r="N170">
-        <v>-2.823481318521223</v>
+        <v>-2.928463117568461</v>
       </c>
       <c r="O170">
-        <v>2.940919324099452</v>
+        <v>2.970502543738218</v>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>[-2.8235, 2.9409]</t>
+          <t>[-2.9285, 2.9705]</t>
         </is>
       </c>
     </row>
@@ -37624,35 +37624,35 @@
         </is>
       </c>
       <c r="G171">
-        <v>0.06435933518172307</v>
+        <v>0.004924393786604308</v>
       </c>
       <c r="H171">
-        <v>1.517795516412117</v>
+        <v>1.499951496960697</v>
       </c>
       <c r="I171">
-        <v>0.02914492561837783</v>
+        <v>0.01713747479339629</v>
       </c>
       <c r="J171">
-        <v>2712.1</v>
+        <v>7660.6</v>
       </c>
       <c r="K171">
-        <v>1.0002</v>
+        <v>1</v>
       </c>
       <c r="L171">
-        <v>1.0004</v>
+        <v>1.0001</v>
       </c>
       <c r="M171">
-        <v>0.09438607583149805</v>
+        <v>0.01355707068034473</v>
       </c>
       <c r="N171">
-        <v>-2.864174275326936</v>
+        <v>-2.977593515416843</v>
       </c>
       <c r="O171">
-        <v>3.019325194908544</v>
+        <v>2.935011954013199</v>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>[-2.8642, 3.0193]</t>
+          <t>[-2.9776, 2.9350]</t>
         </is>
       </c>
     </row>
@@ -37686,35 +37686,35 @@
         </is>
       </c>
       <c r="G172">
-        <v>-0.1889578831058645</v>
+        <v>-0.1831147261014914</v>
       </c>
       <c r="H172">
-        <v>0.1327116504290296</v>
+        <v>0.1350369720875784</v>
       </c>
       <c r="I172">
-        <v>0.004613265392048112</v>
+        <v>0.003828270594696542</v>
       </c>
       <c r="J172">
-        <v>827.6</v>
+        <v>1244.2</v>
       </c>
       <c r="K172">
-        <v>1.0174</v>
+        <v>1.0153</v>
       </c>
       <c r="L172">
-        <v>1.0176</v>
+        <v>1.0154</v>
       </c>
       <c r="M172">
-        <v>-0.1854118738502842</v>
+        <v>-0.1785893086645667</v>
       </c>
       <c r="N172">
-        <v>-0.4602265954673859</v>
+        <v>-0.4649684790586853</v>
       </c>
       <c r="O172">
-        <v>0.0567593032052706</v>
+        <v>0.06508679198580132</v>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>[-0.4602, 0.0568]</t>
+          <t>[-0.4650, 0.0651]</t>
         </is>
       </c>
     </row>
@@ -37748,35 +37748,35 @@
         </is>
       </c>
       <c r="G173">
-        <v>0.9183909914910773</v>
+        <v>0.9350824013936898</v>
       </c>
       <c r="H173">
-        <v>0.1304830711675759</v>
+        <v>0.1287839575270144</v>
       </c>
       <c r="I173">
-        <v>0.007026293369721348</v>
+        <v>0.004804261753485707</v>
       </c>
       <c r="J173">
-        <v>344.9</v>
+        <v>718.6</v>
       </c>
       <c r="K173">
-        <v>1.0142</v>
+        <v>1.0242</v>
       </c>
       <c r="L173">
-        <v>1.0144</v>
+        <v>1.0243</v>
       </c>
       <c r="M173">
-        <v>0.9188769232333426</v>
+        <v>0.9339599256730006</v>
       </c>
       <c r="N173">
-        <v>0.6586142205919907</v>
+        <v>0.6837604478264198</v>
       </c>
       <c r="O173">
-        <v>1.172675806558851</v>
+        <v>1.188425484603933</v>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>[0.6586, 1.1727]</t>
+          <t>[0.6838, 1.1884]</t>
         </is>
       </c>
     </row>
@@ -37810,35 +37810,35 @@
         </is>
       </c>
       <c r="G174">
-        <v>0.6641186302686938</v>
+        <v>0.6642708613975647</v>
       </c>
       <c r="H174">
-        <v>0.002613431798127484</v>
+        <v>0.002357343008159838</v>
       </c>
       <c r="I174">
-        <v>9.175341124116098E-05</v>
+        <v>4.793828315454394E-05</v>
       </c>
       <c r="J174">
-        <v>811.3</v>
+        <v>2418.1</v>
       </c>
       <c r="K174">
-        <v>1.0005</v>
+        <v>1</v>
       </c>
       <c r="L174">
-        <v>1.0007</v>
+        <v>1.0001</v>
       </c>
       <c r="M174">
-        <v>0.6648418865360668</v>
+        <v>0.6649741119374146</v>
       </c>
       <c r="N174">
-        <v>0.65697520273902</v>
+        <v>0.6578967341437028</v>
       </c>
       <c r="O174">
-        <v>0.6666101511910684</v>
+        <v>0.6666050431548127</v>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>[0.6570, 0.6666]</t>
+          <t>[0.6579, 0.6666]</t>
         </is>
       </c>
     </row>
@@ -37872,35 +37872,35 @@
         </is>
       </c>
       <c r="G175">
-        <v>0.3358813697313062</v>
+        <v>0.3357291386024353</v>
       </c>
       <c r="H175">
-        <v>0.002613431798127484</v>
+        <v>0.002357343008159839</v>
       </c>
       <c r="I175">
-        <v>9.175341124116093E-05</v>
+        <v>4.79382831545437E-05</v>
       </c>
       <c r="J175">
-        <v>811.3</v>
+        <v>2418.1</v>
       </c>
       <c r="K175">
-        <v>1.0005</v>
+        <v>1</v>
       </c>
       <c r="L175">
-        <v>1.0007</v>
+        <v>1.0001</v>
       </c>
       <c r="M175">
-        <v>0.3351581134639331</v>
+        <v>0.3350258880625854</v>
       </c>
       <c r="N175">
-        <v>0.3333898488089316</v>
+        <v>0.3333949568451872</v>
       </c>
       <c r="O175">
-        <v>0.34302479726098</v>
+        <v>0.3421032658562973</v>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>[0.3334, 0.3430]</t>
+          <t>[0.3334, 0.3421]</t>
         </is>
       </c>
     </row>
@@ -37934,35 +37934,35 @@
         </is>
       </c>
       <c r="G176">
-        <v>1.011557198215439</v>
+        <v>1.010858184148251</v>
       </c>
       <c r="H176">
-        <v>0.0119555746509837</v>
+        <v>0.01075827224867086</v>
       </c>
       <c r="I176">
-        <v>0.0004212677777112531</v>
+        <v>0.000219121133761507</v>
       </c>
       <c r="J176">
-        <v>805.4</v>
+        <v>2410.6</v>
       </c>
       <c r="K176">
-        <v>1.0005</v>
+        <v>1</v>
       </c>
       <c r="L176">
-        <v>1.0007</v>
+        <v>1.0001</v>
       </c>
       <c r="M176">
-        <v>1.008234048580363</v>
+        <v>1.007635882505233</v>
       </c>
       <c r="N176">
-        <v>1.000254341201513</v>
+        <v>1.000277331438548</v>
       </c>
       <c r="O176">
-        <v>1.044254930367847</v>
+        <v>1.039990770896797</v>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>[1.0003, 1.0443]</t>
+          <t>[1.0003, 1.0400]</t>
         </is>
       </c>
     </row>
@@ -37996,35 +37996,35 @@
         </is>
       </c>
       <c r="G177">
-        <v>0.010370140030249</v>
+        <v>0.01051965244799468</v>
       </c>
       <c r="H177">
-        <v>0.01008191102340146</v>
+        <v>0.01042131091402868</v>
       </c>
       <c r="I177">
-        <v>0.0003071848890371624</v>
+        <v>0.0002162278046251855</v>
       </c>
       <c r="J177">
-        <v>1077.2</v>
+        <v>2322.9</v>
       </c>
       <c r="K177">
-        <v>1.0053</v>
+        <v>1.0002</v>
       </c>
       <c r="L177">
-        <v>1.0055</v>
+        <v>1.0002</v>
       </c>
       <c r="M177">
-        <v>0.007451785075054682</v>
+        <v>0.00730961571359073</v>
       </c>
       <c r="N177">
-        <v>0.0002357512741841461</v>
+        <v>0.00030989753359029</v>
       </c>
       <c r="O177">
-        <v>0.03746074981413403</v>
+        <v>0.03785720046964867</v>
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>[0.0002, 0.0375]</t>
+          <t>[0.0003, 0.0379]</t>
         </is>
       </c>
     </row>
@@ -38058,31 +38058,31 @@
         </is>
       </c>
       <c r="G178">
-        <v>0.1258487896051734</v>
+        <v>0.1258345179695498</v>
       </c>
       <c r="H178">
-        <v>0.0007490006050044072</v>
+        <v>0.0007413213044093456</v>
       </c>
       <c r="I178">
-        <v>2.166112863718679E-05</v>
+        <v>1.287888053140358E-05</v>
       </c>
       <c r="J178">
-        <v>1195.6</v>
+        <v>3313.3</v>
       </c>
       <c r="K178">
-        <v>1</v>
+        <v>1.0007</v>
       </c>
       <c r="L178">
-        <v>1.0002</v>
+        <v>1.0007</v>
       </c>
       <c r="M178">
-        <v>0.1258909119043385</v>
+        <v>0.1258801095792167</v>
       </c>
       <c r="N178">
-        <v>0.1241785296227587</v>
+        <v>0.124240689039838</v>
       </c>
       <c r="O178">
-        <v>0.1271593538523231</v>
+        <v>0.1271622155010821</v>
       </c>
       <c r="P178" t="inlineStr">
         <is>
@@ -38120,35 +38120,35 @@
         </is>
       </c>
       <c r="G179">
-        <v>0.06371704026670297</v>
+        <v>0.06366761678554783</v>
       </c>
       <c r="H179">
-        <v>0.0005841059308387508</v>
+        <v>0.0005342838785689983</v>
       </c>
       <c r="I179">
-        <v>1.988522432268647E-05</v>
+        <v>1.057011493718999E-05</v>
       </c>
       <c r="J179">
-        <v>862.8</v>
+        <v>2555</v>
       </c>
       <c r="K179">
-        <v>1.001</v>
+        <v>1.0001</v>
       </c>
       <c r="L179">
-        <v>1.0011</v>
+        <v>1.0002</v>
       </c>
       <c r="M179">
-        <v>0.06362399146240541</v>
+        <v>0.06359989551439847</v>
       </c>
       <c r="N179">
-        <v>0.0628602662168975</v>
+        <v>0.06284223721399033</v>
       </c>
       <c r="O179">
-        <v>0.06514284886285307</v>
+        <v>0.06497111373474523</v>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>[0.0629, 0.0651]</t>
+          <t>[0.0628, 0.0650]</t>
         </is>
       </c>
     </row>
@@ -38182,35 +38182,35 @@
         </is>
       </c>
       <c r="G180">
-        <v>0.09125447553270249</v>
+        <v>0.09106027021934722</v>
       </c>
       <c r="H180">
-        <v>0.002913049482030947</v>
+        <v>0.002966505740861798</v>
       </c>
       <c r="I180">
-        <v>7.537205934403623E-05</v>
+        <v>4.936275214959514E-05</v>
       </c>
       <c r="J180">
-        <v>1493.7</v>
+        <v>3611.5</v>
       </c>
       <c r="K180">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L180">
-        <v>1.0001</v>
+        <v>1.0009</v>
       </c>
       <c r="M180">
-        <v>0.09122397355060981</v>
+        <v>0.0910640919040135</v>
       </c>
       <c r="N180">
-        <v>0.08563866219184785</v>
+        <v>0.08526749403859259</v>
       </c>
       <c r="O180">
-        <v>0.09711626494942949</v>
+        <v>0.09690547123469559</v>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>[0.0856, 0.0971]</t>
+          <t>[0.0853, 0.0969]</t>
         </is>
       </c>
     </row>
@@ -38244,35 +38244,35 @@
         </is>
       </c>
       <c r="G181">
-        <v>0.04649770199450558</v>
+        <v>0.04637346409278303</v>
       </c>
       <c r="H181">
-        <v>0.001545892051463441</v>
+        <v>0.001542824598922063</v>
       </c>
       <c r="I181">
-        <v>4.369570629977752E-05</v>
+        <v>2.656405055689592E-05</v>
       </c>
       <c r="J181">
-        <v>1251.6</v>
+        <v>3373.2</v>
       </c>
       <c r="K181">
-        <v>1.0007</v>
+        <v>1.0008</v>
       </c>
       <c r="L181">
         <v>1.0009</v>
       </c>
       <c r="M181">
-        <v>0.04648513188188992</v>
+        <v>0.04637223933659133</v>
       </c>
       <c r="N181">
-        <v>0.04357333565288647</v>
+        <v>0.04342574546354662</v>
       </c>
       <c r="O181">
-        <v>0.04956871016918693</v>
+        <v>0.04940846318447061</v>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>[0.0436, 0.0496]</t>
+          <t>[0.0434, 0.0494]</t>
         </is>
       </c>
     </row>
@@ -38306,35 +38306,35 @@
         </is>
       </c>
       <c r="G182">
-        <v>0.04808237925543987</v>
+        <v>0.04779046743573452</v>
       </c>
       <c r="H182">
-        <v>0.004142226875569896</v>
+        <v>0.004193489889832808</v>
       </c>
       <c r="I182">
-        <v>0.0001074884708010635</v>
+        <v>6.979446174698256E-05</v>
       </c>
       <c r="J182">
-        <v>1485.1</v>
+        <v>3610</v>
       </c>
       <c r="K182">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L182">
-        <v>1.0001</v>
+        <v>1.0008</v>
       </c>
       <c r="M182">
-        <v>0.04796774927696158</v>
+        <v>0.04768958444714324</v>
       </c>
       <c r="N182">
-        <v>0.04040227159343468</v>
+        <v>0.03993531581466844</v>
       </c>
       <c r="O182">
-        <v>0.05678648824755204</v>
+        <v>0.05633612355151823</v>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>[0.0404, 0.0568]</t>
+          <t>[0.0399, 0.0563]</t>
         </is>
       </c>
     </row>
@@ -38368,35 +38368,35 @@
         </is>
       </c>
       <c r="G183">
-        <v>0.02481570922370386</v>
+        <v>0.02465735063902469</v>
       </c>
       <c r="H183">
-        <v>0.002174174555693733</v>
+        <v>0.002185132242798985</v>
       </c>
       <c r="I183">
-        <v>5.955577645039159E-05</v>
+        <v>3.756211461109371E-05</v>
       </c>
       <c r="J183">
-        <v>1332.7</v>
+        <v>3384.2</v>
       </c>
       <c r="K183">
-        <v>1.0005</v>
+        <v>1.0009</v>
       </c>
       <c r="L183">
-        <v>1.0006</v>
+        <v>1.0009</v>
       </c>
       <c r="M183">
-        <v>0.02473670745279042</v>
+        <v>0.02458428570939757</v>
       </c>
       <c r="N183">
-        <v>0.02084774505484325</v>
+        <v>0.02059319434918493</v>
       </c>
       <c r="O183">
-        <v>0.02935120201155536</v>
+        <v>0.02915025209641028</v>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>[0.0208, 0.0294]</t>
+          <t>[0.0206, 0.0292]</t>
         </is>
       </c>
     </row>
@@ -38430,35 +38430,35 @@
         </is>
       </c>
       <c r="G184">
-        <v>0.01848769677962476</v>
+        <v>0.01826999464690852</v>
       </c>
       <c r="H184">
-        <v>0.003106155478899864</v>
+        <v>0.003123396598778489</v>
       </c>
       <c r="I184">
-        <v>8.08745923230868E-05</v>
+        <v>5.197740045955485E-05</v>
       </c>
       <c r="J184">
-        <v>1475.1</v>
+        <v>3611</v>
       </c>
       <c r="K184">
-        <v>1</v>
+        <v>1.0007</v>
       </c>
       <c r="L184">
-        <v>1.0001</v>
+        <v>1.0008</v>
       </c>
       <c r="M184">
-        <v>0.01827336822367226</v>
+        <v>0.01805670116753954</v>
       </c>
       <c r="N184">
-        <v>0.01309164932196919</v>
+        <v>0.01279367085685583</v>
       </c>
       <c r="O184">
-        <v>0.02537930596735118</v>
+        <v>0.02499190126033523</v>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>[0.0131, 0.0254]</t>
+          <t>[0.0128, 0.0250]</t>
         </is>
       </c>
     </row>
@@ -38492,35 +38492,35 @@
         </is>
       </c>
       <c r="G185">
-        <v>0.009728033043400539</v>
+        <v>0.009613789963538483</v>
       </c>
       <c r="H185">
-        <v>0.001656559538795364</v>
+        <v>0.001659710961352733</v>
       </c>
       <c r="I185">
-        <v>4.406880200946787E-05</v>
+        <v>2.845605779884202E-05</v>
       </c>
       <c r="J185">
-        <v>1413</v>
+        <v>3401.9</v>
       </c>
       <c r="K185">
-        <v>1.0003</v>
+        <v>1.0009</v>
       </c>
       <c r="L185">
-        <v>1.0005</v>
+        <v>1.0009</v>
       </c>
       <c r="M185">
-        <v>0.009607564608013517</v>
+        <v>0.009493398199156081</v>
       </c>
       <c r="N185">
-        <v>0.006891810434206218</v>
+        <v>0.00671882454729464</v>
       </c>
       <c r="O185">
-        <v>0.01334753109768715</v>
+        <v>0.01321921863808871</v>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>[0.0069, 0.0133]</t>
+          <t>[0.0067, 0.0132]</t>
         </is>
       </c>
     </row>
@@ -38554,35 +38554,35 @@
         </is>
       </c>
       <c r="G186">
-        <v>0.005220234655217587</v>
+        <v>0.005121013944093588</v>
       </c>
       <c r="H186">
-        <v>0.001456598426889403</v>
+        <v>0.001453488374563846</v>
       </c>
       <c r="I186">
-        <v>3.743611694174209E-05</v>
+        <v>2.363191062934687E-05</v>
       </c>
       <c r="J186">
-        <v>1513.9</v>
+        <v>3782.9</v>
       </c>
       <c r="K186">
-        <v>1</v>
+        <v>1.0007</v>
       </c>
       <c r="L186">
-        <v>1.0001</v>
+        <v>1.0008</v>
       </c>
       <c r="M186">
-        <v>0.005041649373712145</v>
+        <v>0.004947582994171094</v>
       </c>
       <c r="N186">
-        <v>0.002908816210252981</v>
+        <v>0.002804708150348499</v>
       </c>
       <c r="O186">
-        <v>0.008674997473004487</v>
+        <v>0.008463912321821093</v>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>[0.0029, 0.0087]</t>
+          <t>[0.0028, 0.0085]</t>
         </is>
       </c>
     </row>
@@ -38616,35 +38616,35 @@
         </is>
       </c>
       <c r="G187">
-        <v>0.002819306852193219</v>
+        <v>0.002767069161681853</v>
       </c>
       <c r="H187">
-        <v>0.0007967959562887942</v>
+        <v>0.000793902227942943</v>
       </c>
       <c r="I187">
-        <v>2.118781498448822E-05</v>
+        <v>1.354901355157748E-05</v>
       </c>
       <c r="J187">
-        <v>1414.2</v>
+        <v>3433.4</v>
       </c>
       <c r="K187">
-        <v>1.0002</v>
+        <v>1.0008</v>
       </c>
       <c r="L187">
-        <v>1.0004</v>
+        <v>1.0009</v>
       </c>
       <c r="M187">
-        <v>0.00272233955576463</v>
+        <v>0.002667922613598113</v>
       </c>
       <c r="N187">
-        <v>0.001574449140007004</v>
+        <v>0.001508436419617021</v>
       </c>
       <c r="O187">
-        <v>0.004684462298961861</v>
+        <v>0.004608940832588046</v>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>[0.0016, 0.0047]</t>
+          <t>[0.0015, 0.0046]</t>
         </is>
       </c>
     </row>
@@ -38678,35 +38678,35 @@
         </is>
       </c>
       <c r="G188">
-        <v>34.86268718595983</v>
+        <v>34.75180857494147</v>
       </c>
       <c r="H188">
-        <v>1.530407767195968</v>
+        <v>1.542203422448353</v>
       </c>
       <c r="I188">
-        <v>0.03986113632044151</v>
+        <v>0.0256884207670004</v>
       </c>
       <c r="J188">
-        <v>1474.1</v>
+        <v>3604.2</v>
       </c>
       <c r="K188">
-        <v>1</v>
+        <v>1.0007</v>
       </c>
       <c r="L188">
-        <v>1.0001</v>
+        <v>1.0008</v>
       </c>
       <c r="M188">
-        <v>34.78650917988247</v>
+        <v>34.68583666260966</v>
       </c>
       <c r="N188">
-        <v>32.10728854093265</v>
+        <v>31.95130069229326</v>
       </c>
       <c r="O188">
-        <v>38.17519138091162</v>
+        <v>37.99284067814255</v>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>[32.1073, 38.1752]</t>
+          <t>[31.9513, 37.9928]</t>
         </is>
       </c>
     </row>
@@ -38740,35 +38740,35 @@
         </is>
       </c>
       <c r="G189">
-        <v>35.2281855078489</v>
+        <v>35.12140768963494</v>
       </c>
       <c r="H189">
-        <v>1.594168463608602</v>
+        <v>1.606142811826278</v>
       </c>
       <c r="I189">
-        <v>0.04224238212950401</v>
+        <v>0.02757379142867065</v>
       </c>
       <c r="J189">
-        <v>1424.2</v>
+        <v>3392.9</v>
       </c>
       <c r="K189">
-        <v>1.0003</v>
+        <v>1.0009</v>
       </c>
       <c r="L189">
-        <v>1.0005</v>
+        <v>1.001</v>
       </c>
       <c r="M189">
-        <v>35.14874543285814</v>
+        <v>35.04006574650231</v>
       </c>
       <c r="N189">
-        <v>32.40047229744872</v>
+        <v>32.22093036707422</v>
       </c>
       <c r="O189">
-        <v>38.64796683131308</v>
+        <v>38.55150317832572</v>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>[32.4005, 38.6480]</t>
+          <t>[32.2209, 38.5515]</t>
         </is>
       </c>
     </row>
@@ -38802,35 +38802,35 @@
         </is>
       </c>
       <c r="G190">
-        <v>3.550458937681949</v>
+        <v>3.547252186736515</v>
       </c>
       <c r="H190">
-        <v>0.04372901139278984</v>
+        <v>0.04421217739188651</v>
       </c>
       <c r="I190">
-        <v>0.001137124478600515</v>
+        <v>0.0007364914160822994</v>
       </c>
       <c r="J190">
-        <v>1478.8</v>
+        <v>3603.7</v>
       </c>
       <c r="K190">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="L190">
-        <v>1.0001</v>
+        <v>1.0008</v>
       </c>
       <c r="M190">
-        <v>3.5492296443733</v>
+        <v>3.546331438288005</v>
       </c>
       <c r="N190">
-        <v>3.469083061712278</v>
+        <v>3.464212890233106</v>
       </c>
       <c r="O190">
-        <v>3.642185864344563</v>
+        <v>3.637397738769497</v>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>[3.4691, 3.6422]</t>
+          <t>[3.4642, 3.6374]</t>
         </is>
       </c>
     </row>
@@ -38864,35 +38864,35 @@
         </is>
       </c>
       <c r="G191">
-        <v>0.4928832352681846</v>
+        <v>0.5216747421585012</v>
       </c>
       <c r="H191">
-        <v>0.2081492105235483</v>
+        <v>0.1656690180157772</v>
       </c>
       <c r="I191">
-        <v>0.09709510846427355</v>
+        <v>0.06033109224899625</v>
       </c>
       <c r="J191">
-        <v>4.6</v>
+        <v>7.5</v>
       </c>
       <c r="K191">
-        <v>1.7787</v>
+        <v>1.0552</v>
       </c>
       <c r="L191">
-        <v>1.779</v>
+        <v>1.0553</v>
       </c>
       <c r="M191">
-        <v>0.4948766498617353</v>
+        <v>0.4970093760277954</v>
       </c>
       <c r="N191">
-        <v>0.194505971157467</v>
+        <v>0.2544938193727065</v>
       </c>
       <c r="O191">
-        <v>1.018700735436573</v>
+        <v>0.867919380982383</v>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>[0.1945, 1.0187]</t>
+          <t>[0.2545, 0.8679]</t>
         </is>
       </c>
     </row>
@@ -38926,35 +38926,35 @@
         </is>
       </c>
       <c r="G192">
-        <v>1.331503182455854E-19</v>
+        <v>1.376033557114029E-19</v>
       </c>
       <c r="H192">
-        <v>0.2938146899795536</v>
+        <v>0.3011703008116224</v>
       </c>
       <c r="I192">
-        <v>0.01247840830639177</v>
+        <v>0.008113966761992346</v>
       </c>
       <c r="J192">
-        <v>580.3</v>
+        <v>1444.2</v>
       </c>
       <c r="K192">
-        <v>1.0151</v>
+        <v>1.0143</v>
       </c>
       <c r="L192">
-        <v>1.3303</v>
+        <v>1.1095</v>
       </c>
       <c r="M192">
-        <v>0.002399851047316747</v>
+        <v>0.00430320814803211</v>
       </c>
       <c r="N192">
-        <v>-0.6464635130175024</v>
+        <v>-0.6663148683183093</v>
       </c>
       <c r="O192">
-        <v>0.6286510644307732</v>
+        <v>0.6420334946231024</v>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>[-0.6465, 0.6287]</t>
+          <t>[-0.6663, 0.6420]</t>
         </is>
       </c>
     </row>
